--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="339">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -706,6 +706,18 @@
     <t>['59', '70']</t>
   </si>
   <si>
+    <t>['13', '90+5']</t>
+  </si>
+  <si>
+    <t>['31', '33', '67']</t>
+  </si>
+  <si>
+    <t>['82', '90+2']</t>
+  </si>
+  <si>
+    <t>['8']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1007,6 +1019,18 @@
   </si>
   <si>
     <t>['7', '44', '90+4']</t>
+  </si>
+  <si>
+    <t>['50', '68']</t>
+  </si>
+  <si>
+    <t>['51', '78']</t>
+  </si>
+  <si>
+    <t>['66', '78']</t>
+  </si>
+  <si>
+    <t>['66']</t>
   </si>
 </sst>
 </file>
@@ -1368,7 +1392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP200"/>
+  <dimension ref="A1:BP204"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1705,7 +1729,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ2">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1830,7 +1854,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -1911,7 +1935,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ3">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2242,7 +2266,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2654,7 +2678,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2732,10 +2756,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2860,7 +2884,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -2938,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ8">
         <v>1.11</v>
@@ -3144,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ9">
         <v>1.11</v>
@@ -3272,7 +3296,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3350,10 +3374,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ10">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3684,7 +3708,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4920,7 +4944,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5126,7 +5150,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5950,7 +5974,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6156,7 +6180,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6237,7 +6261,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ24">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR24">
         <v>0.77</v>
@@ -6440,7 +6464,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ25">
         <v>0.9</v>
@@ -6646,7 +6670,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ26">
         <v>0.2</v>
@@ -6774,7 +6798,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6855,7 +6879,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ27">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR27">
         <v>0.83</v>
@@ -6980,7 +7004,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7058,10 +7082,10 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ28">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR28">
         <v>1.25</v>
@@ -7186,7 +7210,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7264,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ29">
         <v>1.11</v>
@@ -7598,7 +7622,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7679,7 +7703,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ31">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AR31">
         <v>1.62</v>
@@ -7804,7 +7828,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8216,7 +8240,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -9040,7 +9064,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9246,7 +9270,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9452,7 +9476,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9658,7 +9682,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9864,7 +9888,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -9942,7 +9966,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ42">
         <v>1.91</v>
@@ -10070,7 +10094,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10563,7 +10587,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ45">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR45">
         <v>1.78</v>
@@ -11718,7 +11742,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -11924,7 +11948,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12005,7 +12029,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ52">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR52">
         <v>0.75</v>
@@ -12130,7 +12154,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12208,10 +12232,10 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ53">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR53">
         <v>1.65</v>
@@ -12542,7 +12566,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -12826,7 +12850,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ56">
         <v>1.2</v>
@@ -12954,7 +12978,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13032,7 +13056,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ57">
         <v>1.3</v>
@@ -13160,7 +13184,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13241,7 +13265,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ58">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AR58">
         <v>1.42</v>
@@ -13366,7 +13390,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13572,7 +13596,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13778,7 +13802,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -13984,7 +14008,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14065,7 +14089,7 @@
         <v>1</v>
       </c>
       <c r="AQ62">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AR62">
         <v>1.29</v>
@@ -14271,7 +14295,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ63">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR63">
         <v>1.12</v>
@@ -14396,7 +14420,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14477,7 +14501,7 @@
         <v>2</v>
       </c>
       <c r="AQ64">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR64">
         <v>2.4</v>
@@ -14602,7 +14626,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14680,7 +14704,7 @@
         <v>0.67</v>
       </c>
       <c r="AP65">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ65">
         <v>0.9</v>
@@ -14808,7 +14832,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14886,7 +14910,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ66">
         <v>0.9</v>
@@ -15504,7 +15528,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ69">
         <v>2.09</v>
@@ -15838,7 +15862,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16044,7 +16068,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q72">
         <v>1.95</v>
@@ -16250,7 +16274,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16456,7 +16480,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16662,7 +16686,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16868,7 +16892,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17074,7 +17098,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17486,7 +17510,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17567,7 +17591,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ79">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR79">
         <v>1.27</v>
@@ -17692,7 +17716,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -17976,7 +18000,7 @@
         <v>0.33</v>
       </c>
       <c r="AP81">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ81">
         <v>1.11</v>
@@ -18104,7 +18128,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18516,7 +18540,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18722,7 +18746,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -18803,7 +18827,7 @@
         <v>2</v>
       </c>
       <c r="AQ85">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR85">
         <v>1.28</v>
@@ -18928,7 +18952,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19006,7 +19030,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ86">
         <v>0.9</v>
@@ -19215,7 +19239,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ87">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR87">
         <v>1.26</v>
@@ -19340,7 +19364,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19418,7 +19442,7 @@
         <v>1.25</v>
       </c>
       <c r="AP88">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ88">
         <v>1.64</v>
@@ -19752,7 +19776,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -19830,7 +19854,7 @@
         <v>1.25</v>
       </c>
       <c r="AP90">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ90">
         <v>1</v>
@@ -19958,7 +19982,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20039,7 +20063,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ91">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AR91">
         <v>2.46</v>
@@ -20657,7 +20681,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ94">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR94">
         <v>1.6</v>
@@ -21272,7 +21296,7 @@
         <v>1.25</v>
       </c>
       <c r="AP97">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ97">
         <v>1.2</v>
@@ -21400,7 +21424,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21606,7 +21630,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -21812,7 +21836,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22224,7 +22248,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22302,10 +22326,10 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ102">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR102">
         <v>1.76</v>
@@ -22430,7 +22454,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22511,7 +22535,7 @@
         <v>1</v>
       </c>
       <c r="AQ103">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR103">
         <v>1.37</v>
@@ -22714,7 +22738,7 @@
         <v>0.8</v>
       </c>
       <c r="AP104">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ104">
         <v>0.7</v>
@@ -23129,7 +23153,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ106">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR106">
         <v>1.54</v>
@@ -23666,7 +23690,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -23744,7 +23768,7 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ109">
         <v>1.64</v>
@@ -23872,7 +23896,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24078,7 +24102,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q111">
         <v>3.25</v>
@@ -24156,7 +24180,7 @@
         <v>1.4</v>
       </c>
       <c r="AP111">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ111">
         <v>1.73</v>
@@ -24284,7 +24308,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24490,7 +24514,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -25108,7 +25132,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25314,7 +25338,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25520,7 +25544,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25726,7 +25750,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -25807,7 +25831,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ119">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AR119">
         <v>1.07</v>
@@ -25932,7 +25956,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26138,7 +26162,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26344,7 +26368,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26550,7 +26574,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -26631,7 +26655,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ123">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR123">
         <v>1.13</v>
@@ -26834,7 +26858,7 @@
         <v>0.83</v>
       </c>
       <c r="AP124">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ124">
         <v>0.9</v>
@@ -27040,7 +27064,7 @@
         <v>0.83</v>
       </c>
       <c r="AP125">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ125">
         <v>0.5</v>
@@ -27168,7 +27192,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27374,7 +27398,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -27452,7 +27476,7 @@
         <v>1.33</v>
       </c>
       <c r="AP127">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ127">
         <v>1.73</v>
@@ -27864,7 +27888,7 @@
         <v>1.67</v>
       </c>
       <c r="AP129">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ129">
         <v>1.11</v>
@@ -27992,7 +28016,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28073,7 +28097,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ130">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR130">
         <v>1.95</v>
@@ -28279,7 +28303,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ131">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR131">
         <v>1.72</v>
@@ -28404,7 +28428,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28816,7 +28840,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29022,7 +29046,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -29103,7 +29127,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ135">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AR135">
         <v>1.25</v>
@@ -30464,7 +30488,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30545,7 +30569,7 @@
         <v>1</v>
       </c>
       <c r="AQ142">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR142">
         <v>1.38</v>
@@ -30670,7 +30694,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30748,7 +30772,7 @@
         <v>1.29</v>
       </c>
       <c r="AP143">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ143">
         <v>1.64</v>
@@ -31082,7 +31106,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31288,7 +31312,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31494,7 +31518,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31575,7 +31599,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ147">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR147">
         <v>1.16</v>
@@ -31700,7 +31724,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -31906,7 +31930,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32190,7 +32214,7 @@
         <v>0.71</v>
       </c>
       <c r="AP150">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ150">
         <v>0.9</v>
@@ -32318,7 +32342,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -32936,7 +32960,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33017,7 +33041,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ154">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR154">
         <v>1.76</v>
@@ -33142,7 +33166,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33220,7 +33244,7 @@
         <v>1.43</v>
       </c>
       <c r="AP155">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ155">
         <v>1.11</v>
@@ -33348,7 +33372,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33554,7 +33578,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33760,7 +33784,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34044,7 +34068,7 @@
         <v>0.14</v>
       </c>
       <c r="AP159">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ159">
         <v>0.5</v>
@@ -34459,7 +34483,7 @@
         <v>2</v>
       </c>
       <c r="AQ161">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR161">
         <v>1.54</v>
@@ -34584,7 +34608,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34662,7 +34686,7 @@
         <v>1.75</v>
       </c>
       <c r="AP162">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ162">
         <v>2.09</v>
@@ -34790,7 +34814,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -34868,7 +34892,7 @@
         <v>1.38</v>
       </c>
       <c r="AP163">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ163">
         <v>1.3</v>
@@ -34996,7 +35020,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35202,7 +35226,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35614,7 +35638,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35820,7 +35844,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -35901,7 +35925,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ168">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR168">
         <v>1.46</v>
@@ -36232,7 +36256,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36313,7 +36337,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ170">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AR170">
         <v>1.79</v>
@@ -36644,7 +36668,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -36928,7 +36952,7 @@
         <v>1.25</v>
       </c>
       <c r="AP173">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ173">
         <v>1.11</v>
@@ -37262,7 +37286,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -37340,10 +37364,10 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ175">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR175">
         <v>1.78</v>
@@ -37880,7 +37904,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38498,7 +38522,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38579,7 +38603,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ181">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR181">
         <v>1.08</v>
@@ -38704,7 +38728,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39116,7 +39140,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39197,7 +39221,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ184">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR184">
         <v>1.59</v>
@@ -39322,7 +39346,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39528,7 +39552,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -39606,10 +39630,10 @@
         <v>2.5</v>
       </c>
       <c r="AP186">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ186">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AR186">
         <v>1.43</v>
@@ -39940,7 +39964,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40146,7 +40170,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40352,7 +40376,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40430,7 +40454,7 @@
         <v>1.67</v>
       </c>
       <c r="AP190">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ190">
         <v>1.73</v>
@@ -40558,7 +40582,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -40970,7 +40994,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41382,7 +41406,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41588,7 +41612,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -42000,7 +42024,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42206,7 +42230,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42412,7 +42436,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42569,6 +42593,830 @@
       </c>
       <c r="BP200">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="201" spans="1:68">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>7466888</v>
+      </c>
+      <c r="C201" t="s">
+        <v>68</v>
+      </c>
+      <c r="D201" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="2">
+        <v>45671.6875</v>
+      </c>
+      <c r="F201">
+        <v>21</v>
+      </c>
+      <c r="G201" t="s">
+        <v>78</v>
+      </c>
+      <c r="H201" t="s">
+        <v>88</v>
+      </c>
+      <c r="I201">
+        <v>1</v>
+      </c>
+      <c r="J201">
+        <v>0</v>
+      </c>
+      <c r="K201">
+        <v>1</v>
+      </c>
+      <c r="L201">
+        <v>2</v>
+      </c>
+      <c r="M201">
+        <v>2</v>
+      </c>
+      <c r="N201">
+        <v>4</v>
+      </c>
+      <c r="O201" t="s">
+        <v>230</v>
+      </c>
+      <c r="P201" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q201">
+        <v>2.1</v>
+      </c>
+      <c r="R201">
+        <v>2.6</v>
+      </c>
+      <c r="S201">
+        <v>4.75</v>
+      </c>
+      <c r="T201">
+        <v>1.25</v>
+      </c>
+      <c r="U201">
+        <v>3.75</v>
+      </c>
+      <c r="V201">
+        <v>2.2</v>
+      </c>
+      <c r="W201">
+        <v>1.62</v>
+      </c>
+      <c r="X201">
+        <v>5</v>
+      </c>
+      <c r="Y201">
+        <v>1.17</v>
+      </c>
+      <c r="Z201">
+        <v>1.6</v>
+      </c>
+      <c r="AA201">
+        <v>4.5</v>
+      </c>
+      <c r="AB201">
+        <v>4.8</v>
+      </c>
+      <c r="AC201">
+        <v>1.01</v>
+      </c>
+      <c r="AD201">
+        <v>23</v>
+      </c>
+      <c r="AE201">
+        <v>1.14</v>
+      </c>
+      <c r="AF201">
+        <v>6</v>
+      </c>
+      <c r="AG201">
+        <v>1.58</v>
+      </c>
+      <c r="AH201">
+        <v>2.37</v>
+      </c>
+      <c r="AI201">
+        <v>1.5</v>
+      </c>
+      <c r="AJ201">
+        <v>2.5</v>
+      </c>
+      <c r="AK201">
+        <v>1.18</v>
+      </c>
+      <c r="AL201">
+        <v>1.21</v>
+      </c>
+      <c r="AM201">
+        <v>2.25</v>
+      </c>
+      <c r="AN201">
+        <v>1.67</v>
+      </c>
+      <c r="AO201">
+        <v>1.5</v>
+      </c>
+      <c r="AP201">
+        <v>1.6</v>
+      </c>
+      <c r="AQ201">
+        <v>1.45</v>
+      </c>
+      <c r="AR201">
+        <v>1.75</v>
+      </c>
+      <c r="AS201">
+        <v>1.61</v>
+      </c>
+      <c r="AT201">
+        <v>3.36</v>
+      </c>
+      <c r="AU201">
+        <v>11</v>
+      </c>
+      <c r="AV201">
+        <v>4</v>
+      </c>
+      <c r="AW201">
+        <v>16</v>
+      </c>
+      <c r="AX201">
+        <v>4</v>
+      </c>
+      <c r="AY201">
+        <v>36</v>
+      </c>
+      <c r="AZ201">
+        <v>9</v>
+      </c>
+      <c r="BA201">
+        <v>9</v>
+      </c>
+      <c r="BB201">
+        <v>3</v>
+      </c>
+      <c r="BC201">
+        <v>12</v>
+      </c>
+      <c r="BD201">
+        <v>1.42</v>
+      </c>
+      <c r="BE201">
+        <v>7.5</v>
+      </c>
+      <c r="BF201">
+        <v>3.15</v>
+      </c>
+      <c r="BG201">
+        <v>1.11</v>
+      </c>
+      <c r="BH201">
+        <v>5.1</v>
+      </c>
+      <c r="BI201">
+        <v>1.23</v>
+      </c>
+      <c r="BJ201">
+        <v>3.65</v>
+      </c>
+      <c r="BK201">
+        <v>1.41</v>
+      </c>
+      <c r="BL201">
+        <v>2.65</v>
+      </c>
+      <c r="BM201">
+        <v>1.62</v>
+      </c>
+      <c r="BN201">
+        <v>2.12</v>
+      </c>
+      <c r="BO201">
+        <v>1.96</v>
+      </c>
+      <c r="BP201">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="202" spans="1:68">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>7466887</v>
+      </c>
+      <c r="C202" t="s">
+        <v>68</v>
+      </c>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" s="2">
+        <v>45671.6875</v>
+      </c>
+      <c r="F202">
+        <v>21</v>
+      </c>
+      <c r="G202" t="s">
+        <v>76</v>
+      </c>
+      <c r="H202" t="s">
+        <v>83</v>
+      </c>
+      <c r="I202">
+        <v>2</v>
+      </c>
+      <c r="J202">
+        <v>0</v>
+      </c>
+      <c r="K202">
+        <v>2</v>
+      </c>
+      <c r="L202">
+        <v>3</v>
+      </c>
+      <c r="M202">
+        <v>2</v>
+      </c>
+      <c r="N202">
+        <v>5</v>
+      </c>
+      <c r="O202" t="s">
+        <v>231</v>
+      </c>
+      <c r="P202" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q202">
+        <v>3.25</v>
+      </c>
+      <c r="R202">
+        <v>2.25</v>
+      </c>
+      <c r="S202">
+        <v>3</v>
+      </c>
+      <c r="T202">
+        <v>1.33</v>
+      </c>
+      <c r="U202">
+        <v>3.25</v>
+      </c>
+      <c r="V202">
+        <v>2.63</v>
+      </c>
+      <c r="W202">
+        <v>1.44</v>
+      </c>
+      <c r="X202">
+        <v>6.5</v>
+      </c>
+      <c r="Y202">
+        <v>1.11</v>
+      </c>
+      <c r="Z202">
+        <v>2.65</v>
+      </c>
+      <c r="AA202">
+        <v>3.6</v>
+      </c>
+      <c r="AB202">
+        <v>2.45</v>
+      </c>
+      <c r="AC202">
+        <v>1.04</v>
+      </c>
+      <c r="AD202">
+        <v>14</v>
+      </c>
+      <c r="AE202">
+        <v>1.23</v>
+      </c>
+      <c r="AF202">
+        <v>4.35</v>
+      </c>
+      <c r="AG202">
+        <v>1.66</v>
+      </c>
+      <c r="AH202">
+        <v>2.1</v>
+      </c>
+      <c r="AI202">
+        <v>1.57</v>
+      </c>
+      <c r="AJ202">
+        <v>2.25</v>
+      </c>
+      <c r="AK202">
+        <v>1.55</v>
+      </c>
+      <c r="AL202">
+        <v>1.29</v>
+      </c>
+      <c r="AM202">
+        <v>1.43</v>
+      </c>
+      <c r="AN202">
+        <v>1.1</v>
+      </c>
+      <c r="AO202">
+        <v>1.44</v>
+      </c>
+      <c r="AP202">
+        <v>1.27</v>
+      </c>
+      <c r="AQ202">
+        <v>1.3</v>
+      </c>
+      <c r="AR202">
+        <v>1.35</v>
+      </c>
+      <c r="AS202">
+        <v>1.37</v>
+      </c>
+      <c r="AT202">
+        <v>2.72</v>
+      </c>
+      <c r="AU202">
+        <v>4</v>
+      </c>
+      <c r="AV202">
+        <v>6</v>
+      </c>
+      <c r="AW202">
+        <v>1</v>
+      </c>
+      <c r="AX202">
+        <v>16</v>
+      </c>
+      <c r="AY202">
+        <v>5</v>
+      </c>
+      <c r="AZ202">
+        <v>28</v>
+      </c>
+      <c r="BA202">
+        <v>0</v>
+      </c>
+      <c r="BB202">
+        <v>3</v>
+      </c>
+      <c r="BC202">
+        <v>3</v>
+      </c>
+      <c r="BD202">
+        <v>2.05</v>
+      </c>
+      <c r="BE202">
+        <v>6.75</v>
+      </c>
+      <c r="BF202">
+        <v>1.92</v>
+      </c>
+      <c r="BG202">
+        <v>1.17</v>
+      </c>
+      <c r="BH202">
+        <v>4.35</v>
+      </c>
+      <c r="BI202">
+        <v>1.3</v>
+      </c>
+      <c r="BJ202">
+        <v>3.15</v>
+      </c>
+      <c r="BK202">
+        <v>1.49</v>
+      </c>
+      <c r="BL202">
+        <v>2.4</v>
+      </c>
+      <c r="BM202">
+        <v>1.79</v>
+      </c>
+      <c r="BN202">
+        <v>1.9</v>
+      </c>
+      <c r="BO202">
+        <v>2.18</v>
+      </c>
+      <c r="BP202">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="203" spans="1:68">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>7466882</v>
+      </c>
+      <c r="C203" t="s">
+        <v>68</v>
+      </c>
+      <c r="D203" t="s">
+        <v>69</v>
+      </c>
+      <c r="E203" s="2">
+        <v>45671.6875</v>
+      </c>
+      <c r="F203">
+        <v>21</v>
+      </c>
+      <c r="G203" t="s">
+        <v>77</v>
+      </c>
+      <c r="H203" t="s">
+        <v>85</v>
+      </c>
+      <c r="I203">
+        <v>0</v>
+      </c>
+      <c r="J203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>0</v>
+      </c>
+      <c r="L203">
+        <v>2</v>
+      </c>
+      <c r="M203">
+        <v>2</v>
+      </c>
+      <c r="N203">
+        <v>4</v>
+      </c>
+      <c r="O203" t="s">
+        <v>232</v>
+      </c>
+      <c r="P203" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q203">
+        <v>4.33</v>
+      </c>
+      <c r="R203">
+        <v>2.63</v>
+      </c>
+      <c r="S203">
+        <v>2.1</v>
+      </c>
+      <c r="T203">
+        <v>1.22</v>
+      </c>
+      <c r="U203">
+        <v>4</v>
+      </c>
+      <c r="V203">
+        <v>2</v>
+      </c>
+      <c r="W203">
+        <v>1.73</v>
+      </c>
+      <c r="X203">
+        <v>4.33</v>
+      </c>
+      <c r="Y203">
+        <v>1.2</v>
+      </c>
+      <c r="Z203">
+        <v>4.8</v>
+      </c>
+      <c r="AA203">
+        <v>4.5</v>
+      </c>
+      <c r="AB203">
+        <v>1.6</v>
+      </c>
+      <c r="AC203">
+        <v>1.01</v>
+      </c>
+      <c r="AD203">
+        <v>24</v>
+      </c>
+      <c r="AE203">
+        <v>1.12</v>
+      </c>
+      <c r="AF203">
+        <v>6.8</v>
+      </c>
+      <c r="AG203">
+        <v>1.4</v>
+      </c>
+      <c r="AH203">
+        <v>2.9</v>
+      </c>
+      <c r="AI203">
+        <v>1.44</v>
+      </c>
+      <c r="AJ203">
+        <v>2.63</v>
+      </c>
+      <c r="AK203">
+        <v>2.2</v>
+      </c>
+      <c r="AL203">
+        <v>1.2</v>
+      </c>
+      <c r="AM203">
+        <v>1.2</v>
+      </c>
+      <c r="AN203">
+        <v>2.2</v>
+      </c>
+      <c r="AO203">
+        <v>1.4</v>
+      </c>
+      <c r="AP203">
+        <v>2.09</v>
+      </c>
+      <c r="AQ203">
+        <v>1.36</v>
+      </c>
+      <c r="AR203">
+        <v>1.57</v>
+      </c>
+      <c r="AS203">
+        <v>1.8</v>
+      </c>
+      <c r="AT203">
+        <v>3.37</v>
+      </c>
+      <c r="AU203">
+        <v>7</v>
+      </c>
+      <c r="AV203">
+        <v>9</v>
+      </c>
+      <c r="AW203">
+        <v>12</v>
+      </c>
+      <c r="AX203">
+        <v>13</v>
+      </c>
+      <c r="AY203">
+        <v>24</v>
+      </c>
+      <c r="AZ203">
+        <v>25</v>
+      </c>
+      <c r="BA203">
+        <v>4</v>
+      </c>
+      <c r="BB203">
+        <v>5</v>
+      </c>
+      <c r="BC203">
+        <v>9</v>
+      </c>
+      <c r="BD203">
+        <v>4</v>
+      </c>
+      <c r="BE203">
+        <v>8</v>
+      </c>
+      <c r="BF203">
+        <v>1.27</v>
+      </c>
+      <c r="BG203">
+        <v>1.15</v>
+      </c>
+      <c r="BH203">
+        <v>4.6</v>
+      </c>
+      <c r="BI203">
+        <v>1.29</v>
+      </c>
+      <c r="BJ203">
+        <v>3.2</v>
+      </c>
+      <c r="BK203">
+        <v>1.48</v>
+      </c>
+      <c r="BL203">
+        <v>2.43</v>
+      </c>
+      <c r="BM203">
+        <v>1.75</v>
+      </c>
+      <c r="BN203">
+        <v>1.95</v>
+      </c>
+      <c r="BO203">
+        <v>2.15</v>
+      </c>
+      <c r="BP203">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="204" spans="1:68">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7466886</v>
+      </c>
+      <c r="C204" t="s">
+        <v>68</v>
+      </c>
+      <c r="D204" t="s">
+        <v>69</v>
+      </c>
+      <c r="E204" s="2">
+        <v>45671.70833333334</v>
+      </c>
+      <c r="F204">
+        <v>21</v>
+      </c>
+      <c r="G204" t="s">
+        <v>75</v>
+      </c>
+      <c r="H204" t="s">
+        <v>89</v>
+      </c>
+      <c r="I204">
+        <v>1</v>
+      </c>
+      <c r="J204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>1</v>
+      </c>
+      <c r="L204">
+        <v>1</v>
+      </c>
+      <c r="M204">
+        <v>1</v>
+      </c>
+      <c r="N204">
+        <v>2</v>
+      </c>
+      <c r="O204" t="s">
+        <v>233</v>
+      </c>
+      <c r="P204" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q204">
+        <v>4.75</v>
+      </c>
+      <c r="R204">
+        <v>2.38</v>
+      </c>
+      <c r="S204">
+        <v>2.25</v>
+      </c>
+      <c r="T204">
+        <v>1.3</v>
+      </c>
+      <c r="U204">
+        <v>3.4</v>
+      </c>
+      <c r="V204">
+        <v>2.5</v>
+      </c>
+      <c r="W204">
+        <v>1.5</v>
+      </c>
+      <c r="X204">
+        <v>6</v>
+      </c>
+      <c r="Y204">
+        <v>1.13</v>
+      </c>
+      <c r="Z204">
+        <v>5</v>
+      </c>
+      <c r="AA204">
+        <v>4.33</v>
+      </c>
+      <c r="AB204">
+        <v>1.61</v>
+      </c>
+      <c r="AC204">
+        <v>1.03</v>
+      </c>
+      <c r="AD204">
+        <v>17</v>
+      </c>
+      <c r="AE204">
+        <v>1.22</v>
+      </c>
+      <c r="AF204">
+        <v>4.6</v>
+      </c>
+      <c r="AG204">
+        <v>1.68</v>
+      </c>
+      <c r="AH204">
+        <v>2.19</v>
+      </c>
+      <c r="AI204">
+        <v>1.67</v>
+      </c>
+      <c r="AJ204">
+        <v>2.1</v>
+      </c>
+      <c r="AK204">
+        <v>2.05</v>
+      </c>
+      <c r="AL204">
+        <v>1.24</v>
+      </c>
+      <c r="AM204">
+        <v>1.2</v>
+      </c>
+      <c r="AN204">
+        <v>1.89</v>
+      </c>
+      <c r="AO204">
+        <v>2.56</v>
+      </c>
+      <c r="AP204">
+        <v>1.8</v>
+      </c>
+      <c r="AQ204">
+        <v>2.4</v>
+      </c>
+      <c r="AR204">
+        <v>1.5</v>
+      </c>
+      <c r="AS204">
+        <v>1.87</v>
+      </c>
+      <c r="AT204">
+        <v>3.37</v>
+      </c>
+      <c r="AU204">
+        <v>4</v>
+      </c>
+      <c r="AV204">
+        <v>8</v>
+      </c>
+      <c r="AW204">
+        <v>3</v>
+      </c>
+      <c r="AX204">
+        <v>16</v>
+      </c>
+      <c r="AY204">
+        <v>9</v>
+      </c>
+      <c r="AZ204">
+        <v>32</v>
+      </c>
+      <c r="BA204">
+        <v>0</v>
+      </c>
+      <c r="BB204">
+        <v>9</v>
+      </c>
+      <c r="BC204">
+        <v>9</v>
+      </c>
+      <c r="BD204">
+        <v>2.95</v>
+      </c>
+      <c r="BE204">
+        <v>7</v>
+      </c>
+      <c r="BF204">
+        <v>1.47</v>
+      </c>
+      <c r="BG204">
+        <v>1.19</v>
+      </c>
+      <c r="BH204">
+        <v>4.1</v>
+      </c>
+      <c r="BI204">
+        <v>1.33</v>
+      </c>
+      <c r="BJ204">
+        <v>2.95</v>
+      </c>
+      <c r="BK204">
+        <v>1.54</v>
+      </c>
+      <c r="BL204">
+        <v>2.3</v>
+      </c>
+      <c r="BM204">
+        <v>1.86</v>
+      </c>
+      <c r="BN204">
+        <v>1.82</v>
+      </c>
+      <c r="BO204">
+        <v>2.32</v>
+      </c>
+      <c r="BP204">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="342">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -718,6 +718,12 @@
     <t>['8']</t>
   </si>
   <si>
+    <t>['34', '57', '74']</t>
+  </si>
+  <si>
+    <t>['40', '44']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1031,6 +1037,9 @@
   </si>
   <si>
     <t>['66']</t>
+  </si>
+  <si>
+    <t>['52', '78']</t>
   </si>
 </sst>
 </file>
@@ -1392,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP204"/>
+  <dimension ref="A1:BP208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1854,7 +1863,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2138,10 +2147,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ4">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2266,7 +2275,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2344,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ5">
         <v>1.3</v>
@@ -2550,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
         <v>0.2</v>
@@ -2678,7 +2687,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2884,7 +2893,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -2965,7 +2974,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ8">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3171,7 +3180,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ9">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3296,7 +3305,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3580,10 +3589,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ11">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3708,7 +3717,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4944,7 +4953,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5150,7 +5159,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5846,7 +5855,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ22">
         <v>1.3</v>
@@ -5974,7 +5983,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6052,10 +6061,10 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ23">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR23">
         <v>0.86</v>
@@ -6180,7 +6189,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6467,7 +6476,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ25">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR25">
         <v>1.78</v>
@@ -6798,7 +6807,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6876,7 +6885,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ27">
         <v>1.45</v>
@@ -7004,7 +7013,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7210,7 +7219,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7291,7 +7300,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ29">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR29">
         <v>1.08</v>
@@ -7494,10 +7503,10 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR30">
         <v>0.47</v>
@@ -7622,7 +7631,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7828,7 +7837,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8240,7 +8249,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -9064,7 +9073,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9270,7 +9279,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9476,7 +9485,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9682,7 +9691,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9888,7 +9897,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10094,7 +10103,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10378,7 +10387,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ44">
         <v>0.7</v>
@@ -11205,7 +11214,7 @@
         <v>2</v>
       </c>
       <c r="AQ48">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR48">
         <v>1.44</v>
@@ -11742,7 +11751,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -11948,7 +11957,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12026,7 +12035,7 @@
         <v>3</v>
       </c>
       <c r="AP52">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ52">
         <v>1.36</v>
@@ -12154,7 +12163,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12438,10 +12447,10 @@
         <v>0.5</v>
       </c>
       <c r="AP54">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ54">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR54">
         <v>1.48</v>
@@ -12566,7 +12575,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -12644,7 +12653,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ55">
         <v>0.5</v>
@@ -12978,7 +12987,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13184,7 +13193,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13390,7 +13399,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13471,7 +13480,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ59">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR59">
         <v>0.95</v>
@@ -13596,7 +13605,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13677,7 +13686,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ60">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR60">
         <v>1.43</v>
@@ -13802,7 +13811,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14008,7 +14017,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14292,7 +14301,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ63">
         <v>1.45</v>
@@ -14420,7 +14429,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14626,7 +14635,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14832,7 +14841,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14913,7 +14922,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ66">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR66">
         <v>1.43</v>
@@ -15116,7 +15125,7 @@
         <v>0</v>
       </c>
       <c r="AP67">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ67">
         <v>0.2</v>
@@ -15322,7 +15331,7 @@
         <v>1.33</v>
       </c>
       <c r="AP68">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ68">
         <v>1.64</v>
@@ -15862,7 +15871,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -15943,7 +15952,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ71">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR71">
         <v>1.59</v>
@@ -16068,7 +16077,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q72">
         <v>1.95</v>
@@ -16274,7 +16283,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16355,7 +16364,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ73">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR73">
         <v>2.01</v>
@@ -16480,7 +16489,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16686,7 +16695,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16764,7 +16773,7 @@
         <v>1.33</v>
       </c>
       <c r="AP75">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ75">
         <v>1.3</v>
@@ -16892,7 +16901,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17098,7 +17107,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17510,7 +17519,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17716,7 +17725,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18003,7 +18012,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ81">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR81">
         <v>1.42</v>
@@ -18128,7 +18137,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18206,7 +18215,7 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ82">
         <v>2.09</v>
@@ -18540,7 +18549,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18621,7 +18630,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ84">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR84">
         <v>1.51</v>
@@ -18746,7 +18755,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -18952,7 +18961,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19236,7 +19245,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ87">
         <v>1.3</v>
@@ -19364,7 +19373,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19651,7 +19660,7 @@
         <v>1</v>
       </c>
       <c r="AQ89">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR89">
         <v>1.28</v>
@@ -19776,7 +19785,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -19982,7 +19991,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20060,7 +20069,7 @@
         <v>3</v>
       </c>
       <c r="AP91">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ91">
         <v>2.4</v>
@@ -20266,7 +20275,7 @@
         <v>1.75</v>
       </c>
       <c r="AP92">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ92">
         <v>1.73</v>
@@ -21424,7 +21433,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21505,7 +21514,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ98">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR98">
         <v>1.11</v>
@@ -21630,7 +21639,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -21711,7 +21720,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ99">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR99">
         <v>1.99</v>
@@ -21836,7 +21845,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22248,7 +22257,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22454,7 +22463,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23359,7 +23368,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ107">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR107">
         <v>1.75</v>
@@ -23690,7 +23699,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -23896,7 +23905,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24102,7 +24111,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q111">
         <v>3.25</v>
@@ -24308,7 +24317,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24386,7 +24395,7 @@
         <v>2</v>
       </c>
       <c r="AP112">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ112">
         <v>1.91</v>
@@ -24514,7 +24523,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24595,7 +24604,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ113">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR113">
         <v>1.98</v>
@@ -24798,7 +24807,7 @@
         <v>0</v>
       </c>
       <c r="AP114">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ114">
         <v>0.5</v>
@@ -25004,7 +25013,7 @@
         <v>2.2</v>
       </c>
       <c r="AP115">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ115">
         <v>2.09</v>
@@ -25132,7 +25141,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25338,7 +25347,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25419,7 +25428,7 @@
         <v>2</v>
       </c>
       <c r="AQ117">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR117">
         <v>1.41</v>
@@ -25544,7 +25553,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25625,7 +25634,7 @@
         <v>2</v>
       </c>
       <c r="AQ118">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR118">
         <v>2.34</v>
@@ -25750,7 +25759,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -25956,7 +25965,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26162,7 +26171,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26240,7 +26249,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ121">
         <v>1.2</v>
@@ -26368,7 +26377,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26574,7 +26583,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -27192,7 +27201,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27398,7 +27407,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -27891,7 +27900,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ129">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR129">
         <v>1.64</v>
@@ -28016,7 +28025,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28428,7 +28437,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28509,7 +28518,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ132">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR132">
         <v>1.18</v>
@@ -28712,7 +28721,7 @@
         <v>1.33</v>
       </c>
       <c r="AP133">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ133">
         <v>1.2</v>
@@ -28840,7 +28849,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29046,7 +29055,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -29124,7 +29133,7 @@
         <v>2.67</v>
       </c>
       <c r="AP135">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ135">
         <v>2.4</v>
@@ -29536,10 +29545,10 @@
         <v>0.83</v>
       </c>
       <c r="AP137">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ137">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR137">
         <v>1.42</v>
@@ -29948,7 +29957,7 @@
         <v>1</v>
       </c>
       <c r="AP139">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ139">
         <v>1</v>
@@ -30363,7 +30372,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ141">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR141">
         <v>1.64</v>
@@ -30488,7 +30497,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30694,7 +30703,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -31106,7 +31115,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31312,7 +31321,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31518,7 +31527,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31724,7 +31733,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -31802,7 +31811,7 @@
         <v>1.43</v>
       </c>
       <c r="AP148">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ148">
         <v>1.3</v>
@@ -31930,7 +31939,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32217,7 +32226,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ150">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR150">
         <v>1.48</v>
@@ -32342,7 +32351,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -32626,7 +32635,7 @@
         <v>0.71</v>
       </c>
       <c r="AP152">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ152">
         <v>0.7</v>
@@ -32832,7 +32841,7 @@
         <v>0.71</v>
       </c>
       <c r="AP153">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ153">
         <v>0.5</v>
@@ -32960,7 +32969,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33166,7 +33175,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33247,7 +33256,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ155">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR155">
         <v>1.52</v>
@@ -33372,7 +33381,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33453,7 +33462,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ156">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR156">
         <v>1.53</v>
@@ -33578,7 +33587,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33784,7 +33793,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -33865,7 +33874,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ158">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR158">
         <v>1.06</v>
@@ -34608,7 +34617,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34814,7 +34823,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35020,7 +35029,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35226,7 +35235,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35638,7 +35647,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35716,10 +35725,10 @@
         <v>0.63</v>
       </c>
       <c r="AP167">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ167">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR167">
         <v>1.06</v>
@@ -35844,7 +35853,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36128,7 +36137,7 @@
         <v>2.38</v>
       </c>
       <c r="AP169">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ169">
         <v>1.91</v>
@@ -36256,7 +36265,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36668,7 +36677,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -36955,7 +36964,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ173">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR173">
         <v>1.56</v>
@@ -37158,10 +37167,10 @@
         <v>1.25</v>
       </c>
       <c r="AP174">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ174">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR174">
         <v>1.48</v>
@@ -37286,7 +37295,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -37573,7 +37582,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ176">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR176">
         <v>1.74</v>
@@ -37904,7 +37913,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38394,7 +38403,7 @@
         <v>1</v>
       </c>
       <c r="AP180">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ180">
         <v>0.9</v>
@@ -38522,7 +38531,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38600,7 +38609,7 @@
         <v>1.22</v>
       </c>
       <c r="AP181">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ181">
         <v>1.36</v>
@@ -38728,7 +38737,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -38809,7 +38818,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ182">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR182">
         <v>1.74</v>
@@ -39140,7 +39149,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39346,7 +39355,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39424,7 +39433,7 @@
         <v>1.89</v>
       </c>
       <c r="AP185">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ185">
         <v>2.09</v>
@@ -39552,7 +39561,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -39964,7 +39973,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40170,7 +40179,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40376,7 +40385,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40582,7 +40591,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -40994,7 +41003,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41406,7 +41415,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41612,7 +41621,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -42024,7 +42033,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42230,7 +42239,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42436,7 +42445,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42642,7 +42651,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -42848,7 +42857,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43054,7 +43063,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43260,7 +43269,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43417,6 +43426,830 @@
       </c>
       <c r="BP204">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="205" spans="1:68">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>7466885</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" t="s">
+        <v>69</v>
+      </c>
+      <c r="E205" s="2">
+        <v>45672.6875</v>
+      </c>
+      <c r="F205">
+        <v>21</v>
+      </c>
+      <c r="G205" t="s">
+        <v>79</v>
+      </c>
+      <c r="H205" t="s">
+        <v>82</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="J205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>0</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
+      </c>
+      <c r="M205">
+        <v>2</v>
+      </c>
+      <c r="N205">
+        <v>2</v>
+      </c>
+      <c r="O205" t="s">
+        <v>91</v>
+      </c>
+      <c r="P205" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q205">
+        <v>4</v>
+      </c>
+      <c r="R205">
+        <v>2.3</v>
+      </c>
+      <c r="S205">
+        <v>2.5</v>
+      </c>
+      <c r="T205">
+        <v>1.33</v>
+      </c>
+      <c r="U205">
+        <v>3.25</v>
+      </c>
+      <c r="V205">
+        <v>2.63</v>
+      </c>
+      <c r="W205">
+        <v>1.44</v>
+      </c>
+      <c r="X205">
+        <v>6.5</v>
+      </c>
+      <c r="Y205">
+        <v>1.11</v>
+      </c>
+      <c r="Z205">
+        <v>2.98</v>
+      </c>
+      <c r="AA205">
+        <v>3.29</v>
+      </c>
+      <c r="AB205">
+        <v>2.04</v>
+      </c>
+      <c r="AC205">
+        <v>1.04</v>
+      </c>
+      <c r="AD205">
+        <v>14</v>
+      </c>
+      <c r="AE205">
+        <v>1.24</v>
+      </c>
+      <c r="AF205">
+        <v>4.25</v>
+      </c>
+      <c r="AG205">
+        <v>1.75</v>
+      </c>
+      <c r="AH205">
+        <v>2.05</v>
+      </c>
+      <c r="AI205">
+        <v>1.62</v>
+      </c>
+      <c r="AJ205">
+        <v>2.2</v>
+      </c>
+      <c r="AK205">
+        <v>1.78</v>
+      </c>
+      <c r="AL205">
+        <v>1.28</v>
+      </c>
+      <c r="AM205">
+        <v>1.28</v>
+      </c>
+      <c r="AN205">
+        <v>0.9</v>
+      </c>
+      <c r="AO205">
+        <v>1.11</v>
+      </c>
+      <c r="AP205">
+        <v>0.82</v>
+      </c>
+      <c r="AQ205">
+        <v>1.3</v>
+      </c>
+      <c r="AR205">
+        <v>1.11</v>
+      </c>
+      <c r="AS205">
+        <v>1.4</v>
+      </c>
+      <c r="AT205">
+        <v>2.51</v>
+      </c>
+      <c r="AU205">
+        <v>5</v>
+      </c>
+      <c r="AV205">
+        <v>5</v>
+      </c>
+      <c r="AW205">
+        <v>17</v>
+      </c>
+      <c r="AX205">
+        <v>5</v>
+      </c>
+      <c r="AY205">
+        <v>28</v>
+      </c>
+      <c r="AZ205">
+        <v>13</v>
+      </c>
+      <c r="BA205">
+        <v>4</v>
+      </c>
+      <c r="BB205">
+        <v>3</v>
+      </c>
+      <c r="BC205">
+        <v>7</v>
+      </c>
+      <c r="BD205">
+        <v>2.55</v>
+      </c>
+      <c r="BE205">
+        <v>6.75</v>
+      </c>
+      <c r="BF205">
+        <v>1.61</v>
+      </c>
+      <c r="BG205">
+        <v>1.19</v>
+      </c>
+      <c r="BH205">
+        <v>4.1</v>
+      </c>
+      <c r="BI205">
+        <v>1.33</v>
+      </c>
+      <c r="BJ205">
+        <v>2.95</v>
+      </c>
+      <c r="BK205">
+        <v>1.55</v>
+      </c>
+      <c r="BL205">
+        <v>2.28</v>
+      </c>
+      <c r="BM205">
+        <v>1.88</v>
+      </c>
+      <c r="BN205">
+        <v>1.81</v>
+      </c>
+      <c r="BO205">
+        <v>2.33</v>
+      </c>
+      <c r="BP205">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="206" spans="1:68">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>7466889</v>
+      </c>
+      <c r="C206" t="s">
+        <v>68</v>
+      </c>
+      <c r="D206" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="2">
+        <v>45672.6875</v>
+      </c>
+      <c r="F206">
+        <v>21</v>
+      </c>
+      <c r="G206" t="s">
+        <v>74</v>
+      </c>
+      <c r="H206" t="s">
+        <v>87</v>
+      </c>
+      <c r="I206">
+        <v>1</v>
+      </c>
+      <c r="J206">
+        <v>0</v>
+      </c>
+      <c r="K206">
+        <v>1</v>
+      </c>
+      <c r="L206">
+        <v>3</v>
+      </c>
+      <c r="M206">
+        <v>0</v>
+      </c>
+      <c r="N206">
+        <v>3</v>
+      </c>
+      <c r="O206" t="s">
+        <v>234</v>
+      </c>
+      <c r="P206" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q206">
+        <v>1.8</v>
+      </c>
+      <c r="R206">
+        <v>2.75</v>
+      </c>
+      <c r="S206">
+        <v>6.5</v>
+      </c>
+      <c r="T206">
+        <v>1.22</v>
+      </c>
+      <c r="U206">
+        <v>4</v>
+      </c>
+      <c r="V206">
+        <v>2.1</v>
+      </c>
+      <c r="W206">
+        <v>1.67</v>
+      </c>
+      <c r="X206">
+        <v>4.5</v>
+      </c>
+      <c r="Y206">
+        <v>1.18</v>
+      </c>
+      <c r="Z206">
+        <v>1.51</v>
+      </c>
+      <c r="AA206">
+        <v>4.18</v>
+      </c>
+      <c r="AB206">
+        <v>5</v>
+      </c>
+      <c r="AC206">
+        <v>1.01</v>
+      </c>
+      <c r="AD206">
+        <v>25</v>
+      </c>
+      <c r="AE206">
+        <v>1.13</v>
+      </c>
+      <c r="AF206">
+        <v>6.4</v>
+      </c>
+      <c r="AG206">
+        <v>1.45</v>
+      </c>
+      <c r="AH206">
+        <v>2.7</v>
+      </c>
+      <c r="AI206">
+        <v>1.67</v>
+      </c>
+      <c r="AJ206">
+        <v>2.1</v>
+      </c>
+      <c r="AK206">
+        <v>1.09</v>
+      </c>
+      <c r="AL206">
+        <v>1.15</v>
+      </c>
+      <c r="AM206">
+        <v>3.1</v>
+      </c>
+      <c r="AN206">
+        <v>1.89</v>
+      </c>
+      <c r="AO206">
+        <v>0.9</v>
+      </c>
+      <c r="AP206">
+        <v>2</v>
+      </c>
+      <c r="AQ206">
+        <v>0.82</v>
+      </c>
+      <c r="AR206">
+        <v>1.56</v>
+      </c>
+      <c r="AS206">
+        <v>1.22</v>
+      </c>
+      <c r="AT206">
+        <v>2.78</v>
+      </c>
+      <c r="AU206">
+        <v>6</v>
+      </c>
+      <c r="AV206">
+        <v>8</v>
+      </c>
+      <c r="AW206">
+        <v>12</v>
+      </c>
+      <c r="AX206">
+        <v>6</v>
+      </c>
+      <c r="AY206">
+        <v>25</v>
+      </c>
+      <c r="AZ206">
+        <v>16</v>
+      </c>
+      <c r="BA206">
+        <v>4</v>
+      </c>
+      <c r="BB206">
+        <v>2</v>
+      </c>
+      <c r="BC206">
+        <v>6</v>
+      </c>
+      <c r="BD206">
+        <v>1.16</v>
+      </c>
+      <c r="BE206">
+        <v>10</v>
+      </c>
+      <c r="BF206">
+        <v>5.4</v>
+      </c>
+      <c r="BG206">
+        <v>1.15</v>
+      </c>
+      <c r="BH206">
+        <v>4.6</v>
+      </c>
+      <c r="BI206">
+        <v>1.26</v>
+      </c>
+      <c r="BJ206">
+        <v>3.4</v>
+      </c>
+      <c r="BK206">
+        <v>1.44</v>
+      </c>
+      <c r="BL206">
+        <v>2.55</v>
+      </c>
+      <c r="BM206">
+        <v>1.68</v>
+      </c>
+      <c r="BN206">
+        <v>2.04</v>
+      </c>
+      <c r="BO206">
+        <v>2.02</v>
+      </c>
+      <c r="BP206">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="207" spans="1:68">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>7466883</v>
+      </c>
+      <c r="C207" t="s">
+        <v>68</v>
+      </c>
+      <c r="D207" t="s">
+        <v>69</v>
+      </c>
+      <c r="E207" s="2">
+        <v>45672.6875</v>
+      </c>
+      <c r="F207">
+        <v>21</v>
+      </c>
+      <c r="G207" t="s">
+        <v>73</v>
+      </c>
+      <c r="H207" t="s">
+        <v>86</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+      <c r="J207">
+        <v>0</v>
+      </c>
+      <c r="K207">
+        <v>0</v>
+      </c>
+      <c r="L207">
+        <v>0</v>
+      </c>
+      <c r="M207">
+        <v>1</v>
+      </c>
+      <c r="N207">
+        <v>1</v>
+      </c>
+      <c r="O207" t="s">
+        <v>91</v>
+      </c>
+      <c r="P207" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q207">
+        <v>3.75</v>
+      </c>
+      <c r="R207">
+        <v>2.1</v>
+      </c>
+      <c r="S207">
+        <v>3</v>
+      </c>
+      <c r="T207">
+        <v>1.44</v>
+      </c>
+      <c r="U207">
+        <v>2.63</v>
+      </c>
+      <c r="V207">
+        <v>3.25</v>
+      </c>
+      <c r="W207">
+        <v>1.33</v>
+      </c>
+      <c r="X207">
+        <v>9</v>
+      </c>
+      <c r="Y207">
+        <v>1.07</v>
+      </c>
+      <c r="Z207">
+        <v>3.11</v>
+      </c>
+      <c r="AA207">
+        <v>3.16</v>
+      </c>
+      <c r="AB207">
+        <v>2.04</v>
+      </c>
+      <c r="AC207">
+        <v>1.08</v>
+      </c>
+      <c r="AD207">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE207">
+        <v>1.37</v>
+      </c>
+      <c r="AF207">
+        <v>3.25</v>
+      </c>
+      <c r="AG207">
+        <v>1.95</v>
+      </c>
+      <c r="AH207">
+        <v>1.91</v>
+      </c>
+      <c r="AI207">
+        <v>1.8</v>
+      </c>
+      <c r="AJ207">
+        <v>1.95</v>
+      </c>
+      <c r="AK207">
+        <v>1.57</v>
+      </c>
+      <c r="AL207">
+        <v>1.33</v>
+      </c>
+      <c r="AM207">
+        <v>1.36</v>
+      </c>
+      <c r="AN207">
+        <v>1.11</v>
+      </c>
+      <c r="AO207">
+        <v>1.11</v>
+      </c>
+      <c r="AP207">
+        <v>1</v>
+      </c>
+      <c r="AQ207">
+        <v>1.3</v>
+      </c>
+      <c r="AR207">
+        <v>1.34</v>
+      </c>
+      <c r="AS207">
+        <v>1.12</v>
+      </c>
+      <c r="AT207">
+        <v>2.46</v>
+      </c>
+      <c r="AU207">
+        <v>4</v>
+      </c>
+      <c r="AV207">
+        <v>4</v>
+      </c>
+      <c r="AW207">
+        <v>7</v>
+      </c>
+      <c r="AX207">
+        <v>8</v>
+      </c>
+      <c r="AY207">
+        <v>14</v>
+      </c>
+      <c r="AZ207">
+        <v>16</v>
+      </c>
+      <c r="BA207">
+        <v>8</v>
+      </c>
+      <c r="BB207">
+        <v>5</v>
+      </c>
+      <c r="BC207">
+        <v>13</v>
+      </c>
+      <c r="BD207">
+        <v>2.48</v>
+      </c>
+      <c r="BE207">
+        <v>6.75</v>
+      </c>
+      <c r="BF207">
+        <v>1.64</v>
+      </c>
+      <c r="BG207">
+        <v>1.24</v>
+      </c>
+      <c r="BH207">
+        <v>3.55</v>
+      </c>
+      <c r="BI207">
+        <v>1.41</v>
+      </c>
+      <c r="BJ207">
+        <v>2.65</v>
+      </c>
+      <c r="BK207">
+        <v>1.68</v>
+      </c>
+      <c r="BL207">
+        <v>2.04</v>
+      </c>
+      <c r="BM207">
+        <v>2.05</v>
+      </c>
+      <c r="BN207">
+        <v>1.67</v>
+      </c>
+      <c r="BO207">
+        <v>2.55</v>
+      </c>
+      <c r="BP207">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="208" spans="1:68">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>7466881</v>
+      </c>
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" t="s">
+        <v>69</v>
+      </c>
+      <c r="E208" s="2">
+        <v>45672.70833333334</v>
+      </c>
+      <c r="F208">
+        <v>21</v>
+      </c>
+      <c r="G208" t="s">
+        <v>72</v>
+      </c>
+      <c r="H208" t="s">
+        <v>81</v>
+      </c>
+      <c r="I208">
+        <v>2</v>
+      </c>
+      <c r="J208">
+        <v>1</v>
+      </c>
+      <c r="K208">
+        <v>3</v>
+      </c>
+      <c r="L208">
+        <v>2</v>
+      </c>
+      <c r="M208">
+        <v>1</v>
+      </c>
+      <c r="N208">
+        <v>3</v>
+      </c>
+      <c r="O208" t="s">
+        <v>235</v>
+      </c>
+      <c r="P208" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q208">
+        <v>1.8</v>
+      </c>
+      <c r="R208">
+        <v>2.75</v>
+      </c>
+      <c r="S208">
+        <v>6</v>
+      </c>
+      <c r="T208">
+        <v>1.22</v>
+      </c>
+      <c r="U208">
+        <v>4</v>
+      </c>
+      <c r="V208">
+        <v>2</v>
+      </c>
+      <c r="W208">
+        <v>1.73</v>
+      </c>
+      <c r="X208">
+        <v>4.33</v>
+      </c>
+      <c r="Y208">
+        <v>1.2</v>
+      </c>
+      <c r="Z208">
+        <v>1.49</v>
+      </c>
+      <c r="AA208">
+        <v>4.27</v>
+      </c>
+      <c r="AB208">
+        <v>5</v>
+      </c>
+      <c r="AC208">
+        <v>1.01</v>
+      </c>
+      <c r="AD208">
+        <v>27</v>
+      </c>
+      <c r="AE208">
+        <v>1.14</v>
+      </c>
+      <c r="AF208">
+        <v>6.2</v>
+      </c>
+      <c r="AG208">
+        <v>1.36</v>
+      </c>
+      <c r="AH208">
+        <v>3.1</v>
+      </c>
+      <c r="AI208">
+        <v>1.62</v>
+      </c>
+      <c r="AJ208">
+        <v>2.2</v>
+      </c>
+      <c r="AK208">
+        <v>1.1</v>
+      </c>
+      <c r="AL208">
+        <v>1.16</v>
+      </c>
+      <c r="AM208">
+        <v>3</v>
+      </c>
+      <c r="AN208">
+        <v>2.33</v>
+      </c>
+      <c r="AO208">
+        <v>1.11</v>
+      </c>
+      <c r="AP208">
+        <v>2.4</v>
+      </c>
+      <c r="AQ208">
+        <v>1</v>
+      </c>
+      <c r="AR208">
+        <v>1.98</v>
+      </c>
+      <c r="AS208">
+        <v>1.67</v>
+      </c>
+      <c r="AT208">
+        <v>3.65</v>
+      </c>
+      <c r="AU208">
+        <v>5</v>
+      </c>
+      <c r="AV208">
+        <v>3</v>
+      </c>
+      <c r="AW208">
+        <v>10</v>
+      </c>
+      <c r="AX208">
+        <v>8</v>
+      </c>
+      <c r="AY208">
+        <v>24</v>
+      </c>
+      <c r="AZ208">
+        <v>13</v>
+      </c>
+      <c r="BA208">
+        <v>10</v>
+      </c>
+      <c r="BB208">
+        <v>4</v>
+      </c>
+      <c r="BC208">
+        <v>14</v>
+      </c>
+      <c r="BD208">
+        <v>1.25</v>
+      </c>
+      <c r="BE208">
+        <v>8.5</v>
+      </c>
+      <c r="BF208">
+        <v>4.1</v>
+      </c>
+      <c r="BG208">
+        <v>1.17</v>
+      </c>
+      <c r="BH208">
+        <v>4.35</v>
+      </c>
+      <c r="BI208">
+        <v>1.29</v>
+      </c>
+      <c r="BJ208">
+        <v>3.15</v>
+      </c>
+      <c r="BK208">
+        <v>1.49</v>
+      </c>
+      <c r="BL208">
+        <v>2.4</v>
+      </c>
+      <c r="BM208">
+        <v>1.77</v>
+      </c>
+      <c r="BN208">
+        <v>1.92</v>
+      </c>
+      <c r="BO208">
+        <v>2.17</v>
+      </c>
+      <c r="BP208">
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="344">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -724,6 +724,9 @@
     <t>['40', '44']</t>
   </si>
   <si>
+    <t>['82', '90', '90+4']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1040,6 +1043,9 @@
   </si>
   <si>
     <t>['52', '78']</t>
+  </si>
+  <si>
+    <t>['59', '81']</t>
   </si>
 </sst>
 </file>
@@ -1401,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP208"/>
+  <dimension ref="A1:BP210"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1735,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ2">
         <v>1.3</v>
@@ -1863,7 +1869,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -1941,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ3">
         <v>2.4</v>
@@ -2275,7 +2281,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2356,7 +2362,7 @@
         <v>1</v>
       </c>
       <c r="AQ5">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2562,7 +2568,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2687,7 +2693,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2893,7 +2899,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3305,7 +3311,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3717,7 +3723,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4953,7 +4959,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5159,7 +5165,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5858,7 +5864,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ22">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR22">
         <v>1.72</v>
@@ -5983,7 +5989,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6189,7 +6195,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6267,7 +6273,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ24">
         <v>1.3</v>
@@ -6682,7 +6688,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ26">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR26">
         <v>1.29</v>
@@ -6807,7 +6813,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7013,7 +7019,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7219,7 +7225,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7631,7 +7637,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7709,7 +7715,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ31">
         <v>2.4</v>
@@ -7837,7 +7843,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8249,7 +8255,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -9073,7 +9079,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9279,7 +9285,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9485,7 +9491,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9691,7 +9697,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9897,7 +9903,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10103,7 +10109,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -11751,7 +11757,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -11957,7 +11963,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12163,7 +12169,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12575,7 +12581,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -12987,7 +12993,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13068,7 +13074,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ57">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR57">
         <v>1.39</v>
@@ -13193,7 +13199,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13399,7 +13405,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13477,7 +13483,7 @@
         <v>3</v>
       </c>
       <c r="AP59">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ59">
         <v>1.3</v>
@@ -13605,7 +13611,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13683,7 +13689,7 @@
         <v>0.5</v>
       </c>
       <c r="AP60">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ60">
         <v>1</v>
@@ -13811,7 +13817,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -13892,7 +13898,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ61">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR61">
         <v>1.76</v>
@@ -14017,7 +14023,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14429,7 +14435,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14635,7 +14641,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14841,7 +14847,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -15128,7 +15134,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ67">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR67">
         <v>2.4</v>
@@ -15871,7 +15877,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16077,7 +16083,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q72">
         <v>1.95</v>
@@ -16283,7 +16289,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16489,7 +16495,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16567,7 +16573,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ74">
         <v>0.5</v>
@@ -16695,7 +16701,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16776,7 +16782,7 @@
         <v>2</v>
       </c>
       <c r="AQ75">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR75">
         <v>0.91</v>
@@ -16901,7 +16907,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17107,7 +17113,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17185,7 +17191,7 @@
         <v>0.33</v>
       </c>
       <c r="AP77">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ77">
         <v>0.7</v>
@@ -17519,7 +17525,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17725,7 +17731,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18137,7 +18143,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18424,7 +18430,7 @@
         <v>2</v>
       </c>
       <c r="AQ83">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR83">
         <v>2.31</v>
@@ -18549,7 +18555,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18755,7 +18761,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -18961,7 +18967,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19373,7 +19379,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19785,7 +19791,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -19991,7 +19997,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20893,7 +20899,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ95">
         <v>0.5</v>
@@ -21102,7 +21108,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ96">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR96">
         <v>1.78</v>
@@ -21433,7 +21439,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21639,7 +21645,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -21845,7 +21851,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -21923,7 +21929,7 @@
         <v>2.25</v>
       </c>
       <c r="AP100">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ100">
         <v>1.91</v>
@@ -22257,7 +22263,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22463,7 +22469,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22956,7 +22962,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ105">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR105">
         <v>1.17</v>
@@ -23571,7 +23577,7 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ108">
         <v>0.5</v>
@@ -23699,7 +23705,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -23905,7 +23911,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24111,7 +24117,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q111">
         <v>3.25</v>
@@ -24317,7 +24323,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24523,7 +24529,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -25141,7 +25147,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25222,7 +25228,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ116">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR116">
         <v>1.57</v>
@@ -25347,7 +25353,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25553,7 +25559,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25759,7 +25765,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -25965,7 +25971,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26043,7 +26049,7 @@
         <v>1</v>
       </c>
       <c r="AP120">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ120">
         <v>1</v>
@@ -26171,7 +26177,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26377,7 +26383,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26458,7 +26464,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ122">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR122">
         <v>1.46</v>
@@ -26583,7 +26589,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -27201,7 +27207,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27407,7 +27413,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -27691,7 +27697,7 @@
         <v>0.83</v>
       </c>
       <c r="AP128">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ128">
         <v>0.7</v>
@@ -28025,7 +28031,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28437,7 +28443,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28515,7 +28521,7 @@
         <v>0.5</v>
       </c>
       <c r="AP132">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ132">
         <v>1.3</v>
@@ -28849,7 +28855,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29055,7 +29061,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -30166,7 +30172,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ140">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR140">
         <v>1.88</v>
@@ -30497,7 +30503,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30703,7 +30709,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30990,7 +30996,7 @@
         <v>2</v>
       </c>
       <c r="AQ144">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR144">
         <v>1.54</v>
@@ -31115,7 +31121,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31193,7 +31199,7 @@
         <v>1.57</v>
       </c>
       <c r="AP145">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ145">
         <v>2.09</v>
@@ -31321,7 +31327,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31527,7 +31533,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31605,7 +31611,7 @@
         <v>1.14</v>
       </c>
       <c r="AP147">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ147">
         <v>1.45</v>
@@ -31733,7 +31739,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -31814,7 +31820,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ148">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR148">
         <v>1.08</v>
@@ -31939,7 +31945,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32351,7 +32357,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -32969,7 +32975,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33175,7 +33181,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33381,7 +33387,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33587,7 +33593,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33793,7 +33799,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34617,7 +34623,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34823,7 +34829,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -34904,7 +34910,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ163">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR163">
         <v>1.48</v>
@@ -35029,7 +35035,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35107,7 +35113,7 @@
         <v>1.13</v>
       </c>
       <c r="AP164">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ164">
         <v>1.64</v>
@@ -35235,7 +35241,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35522,7 +35528,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ166">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR166">
         <v>1.59</v>
@@ -35647,7 +35653,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35853,7 +35859,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -35931,7 +35937,7 @@
         <v>1.38</v>
       </c>
       <c r="AP168">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ168">
         <v>1.45</v>
@@ -36265,7 +36271,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36677,7 +36683,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37295,7 +37301,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -37913,7 +37919,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38531,7 +38537,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38737,7 +38743,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39024,7 +39030,7 @@
         <v>1</v>
       </c>
       <c r="AQ183">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR183">
         <v>1.34</v>
@@ -39149,7 +39155,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39355,7 +39361,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39561,7 +39567,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -39845,7 +39851,7 @@
         <v>2.22</v>
       </c>
       <c r="AP187">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ187">
         <v>1.91</v>
@@ -39973,7 +39979,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40054,7 +40060,7 @@
         <v>2</v>
       </c>
       <c r="AQ188">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR188">
         <v>1.51</v>
@@ -40179,7 +40185,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40257,7 +40263,7 @@
         <v>1.33</v>
       </c>
       <c r="AP189">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ189">
         <v>1.64</v>
@@ -40385,7 +40391,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40591,7 +40597,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -41003,7 +41009,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41415,7 +41421,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41621,7 +41627,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -42033,7 +42039,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42239,7 +42245,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42445,7 +42451,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42651,7 +42657,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -42857,7 +42863,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43063,7 +43069,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43269,7 +43275,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43475,7 +43481,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -43887,7 +43893,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44250,6 +44256,418 @@
       </c>
       <c r="BP208">
         <v>1.6</v>
+      </c>
+    </row>
+    <row r="209" spans="1:68">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>7466884</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="2">
+        <v>45673.6875</v>
+      </c>
+      <c r="F209">
+        <v>21</v>
+      </c>
+      <c r="G209" t="s">
+        <v>71</v>
+      </c>
+      <c r="H209" t="s">
+        <v>80</v>
+      </c>
+      <c r="I209">
+        <v>0</v>
+      </c>
+      <c r="J209">
+        <v>0</v>
+      </c>
+      <c r="K209">
+        <v>0</v>
+      </c>
+      <c r="L209">
+        <v>0</v>
+      </c>
+      <c r="M209">
+        <v>2</v>
+      </c>
+      <c r="N209">
+        <v>2</v>
+      </c>
+      <c r="O209" t="s">
+        <v>91</v>
+      </c>
+      <c r="P209" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q209">
+        <v>4</v>
+      </c>
+      <c r="R209">
+        <v>2.3</v>
+      </c>
+      <c r="S209">
+        <v>2.5</v>
+      </c>
+      <c r="T209">
+        <v>1.33</v>
+      </c>
+      <c r="U209">
+        <v>3.25</v>
+      </c>
+      <c r="V209">
+        <v>2.5</v>
+      </c>
+      <c r="W209">
+        <v>1.5</v>
+      </c>
+      <c r="X209">
+        <v>6.5</v>
+      </c>
+      <c r="Y209">
+        <v>1.11</v>
+      </c>
+      <c r="Z209">
+        <v>4</v>
+      </c>
+      <c r="AA209">
+        <v>3.95</v>
+      </c>
+      <c r="AB209">
+        <v>1.9</v>
+      </c>
+      <c r="AC209">
+        <v>1.04</v>
+      </c>
+      <c r="AD209">
+        <v>15</v>
+      </c>
+      <c r="AE209">
+        <v>1.23</v>
+      </c>
+      <c r="AF209">
+        <v>4.35</v>
+      </c>
+      <c r="AG209">
+        <v>1.72</v>
+      </c>
+      <c r="AH209">
+        <v>2.18</v>
+      </c>
+      <c r="AI209">
+        <v>1.62</v>
+      </c>
+      <c r="AJ209">
+        <v>2.2</v>
+      </c>
+      <c r="AK209">
+        <v>1.87</v>
+      </c>
+      <c r="AL209">
+        <v>1.27</v>
+      </c>
+      <c r="AM209">
+        <v>1.25</v>
+      </c>
+      <c r="AN209">
+        <v>0.7</v>
+      </c>
+      <c r="AO209">
+        <v>1.3</v>
+      </c>
+      <c r="AP209">
+        <v>0.64</v>
+      </c>
+      <c r="AQ209">
+        <v>1.45</v>
+      </c>
+      <c r="AR209">
+        <v>1.16</v>
+      </c>
+      <c r="AS209">
+        <v>1.39</v>
+      </c>
+      <c r="AT209">
+        <v>2.55</v>
+      </c>
+      <c r="AU209">
+        <v>4</v>
+      </c>
+      <c r="AV209">
+        <v>6</v>
+      </c>
+      <c r="AW209">
+        <v>2</v>
+      </c>
+      <c r="AX209">
+        <v>6</v>
+      </c>
+      <c r="AY209">
+        <v>7</v>
+      </c>
+      <c r="AZ209">
+        <v>16</v>
+      </c>
+      <c r="BA209">
+        <v>1</v>
+      </c>
+      <c r="BB209">
+        <v>9</v>
+      </c>
+      <c r="BC209">
+        <v>10</v>
+      </c>
+      <c r="BD209">
+        <v>2.4</v>
+      </c>
+      <c r="BE209">
+        <v>6.75</v>
+      </c>
+      <c r="BF209">
+        <v>1.68</v>
+      </c>
+      <c r="BG209">
+        <v>1.19</v>
+      </c>
+      <c r="BH209">
+        <v>4.1</v>
+      </c>
+      <c r="BI209">
+        <v>1.32</v>
+      </c>
+      <c r="BJ209">
+        <v>3.05</v>
+      </c>
+      <c r="BK209">
+        <v>1.53</v>
+      </c>
+      <c r="BL209">
+        <v>2.3</v>
+      </c>
+      <c r="BM209">
+        <v>1.84</v>
+      </c>
+      <c r="BN209">
+        <v>1.84</v>
+      </c>
+      <c r="BO209">
+        <v>2.3</v>
+      </c>
+      <c r="BP209">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="210" spans="1:68">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>7466890</v>
+      </c>
+      <c r="C210" t="s">
+        <v>68</v>
+      </c>
+      <c r="D210" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="2">
+        <v>45673.70833333334</v>
+      </c>
+      <c r="F210">
+        <v>21</v>
+      </c>
+      <c r="G210" t="s">
+        <v>70</v>
+      </c>
+      <c r="H210" t="s">
+        <v>84</v>
+      </c>
+      <c r="I210">
+        <v>0</v>
+      </c>
+      <c r="J210">
+        <v>1</v>
+      </c>
+      <c r="K210">
+        <v>1</v>
+      </c>
+      <c r="L210">
+        <v>3</v>
+      </c>
+      <c r="M210">
+        <v>1</v>
+      </c>
+      <c r="N210">
+        <v>4</v>
+      </c>
+      <c r="O210" t="s">
+        <v>236</v>
+      </c>
+      <c r="P210" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q210">
+        <v>1.73</v>
+      </c>
+      <c r="R210">
+        <v>2.63</v>
+      </c>
+      <c r="S210">
+        <v>7.5</v>
+      </c>
+      <c r="T210">
+        <v>1.25</v>
+      </c>
+      <c r="U210">
+        <v>3.75</v>
+      </c>
+      <c r="V210">
+        <v>2.2</v>
+      </c>
+      <c r="W210">
+        <v>1.62</v>
+      </c>
+      <c r="X210">
+        <v>5</v>
+      </c>
+      <c r="Y210">
+        <v>1.17</v>
+      </c>
+      <c r="Z210">
+        <v>1.29</v>
+      </c>
+      <c r="AA210">
+        <v>6.4</v>
+      </c>
+      <c r="AB210">
+        <v>10</v>
+      </c>
+      <c r="AC210">
+        <v>1.01</v>
+      </c>
+      <c r="AD210">
+        <v>24</v>
+      </c>
+      <c r="AE210">
+        <v>1.16</v>
+      </c>
+      <c r="AF210">
+        <v>5.7</v>
+      </c>
+      <c r="AG210">
+        <v>1.74</v>
+      </c>
+      <c r="AH210">
+        <v>2.1</v>
+      </c>
+      <c r="AI210">
+        <v>1.91</v>
+      </c>
+      <c r="AJ210">
+        <v>1.91</v>
+      </c>
+      <c r="AK210">
+        <v>1.06</v>
+      </c>
+      <c r="AL210">
+        <v>1.14</v>
+      </c>
+      <c r="AM210">
+        <v>3.5</v>
+      </c>
+      <c r="AN210">
+        <v>1.3</v>
+      </c>
+      <c r="AO210">
+        <v>0.2</v>
+      </c>
+      <c r="AP210">
+        <v>1.45</v>
+      </c>
+      <c r="AQ210">
+        <v>0.18</v>
+      </c>
+      <c r="AR210">
+        <v>1.48</v>
+      </c>
+      <c r="AS210">
+        <v>0.96</v>
+      </c>
+      <c r="AT210">
+        <v>2.44</v>
+      </c>
+      <c r="AU210">
+        <v>10</v>
+      </c>
+      <c r="AV210">
+        <v>6</v>
+      </c>
+      <c r="AW210">
+        <v>14</v>
+      </c>
+      <c r="AX210">
+        <v>8</v>
+      </c>
+      <c r="AY210">
+        <v>35</v>
+      </c>
+      <c r="AZ210">
+        <v>18</v>
+      </c>
+      <c r="BA210">
+        <v>4</v>
+      </c>
+      <c r="BB210">
+        <v>4</v>
+      </c>
+      <c r="BC210">
+        <v>8</v>
+      </c>
+      <c r="BD210">
+        <v>1.24</v>
+      </c>
+      <c r="BE210">
+        <v>8</v>
+      </c>
+      <c r="BF210">
+        <v>4.35</v>
+      </c>
+      <c r="BG210">
+        <v>1.19</v>
+      </c>
+      <c r="BH210">
+        <v>4.1</v>
+      </c>
+      <c r="BI210">
+        <v>1.34</v>
+      </c>
+      <c r="BJ210">
+        <v>2.9</v>
+      </c>
+      <c r="BK210">
+        <v>1.56</v>
+      </c>
+      <c r="BL210">
+        <v>2.23</v>
+      </c>
+      <c r="BM210">
+        <v>1.88</v>
+      </c>
+      <c r="BN210">
+        <v>1.81</v>
+      </c>
+      <c r="BO210">
+        <v>2.32</v>
+      </c>
+      <c r="BP210">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="350">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -727,6 +727,9 @@
     <t>['82', '90', '90+4']</t>
   </si>
   <si>
+    <t>['35', '55']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1045,7 +1048,22 @@
     <t>['52', '78']</t>
   </si>
   <si>
-    <t>['59', '81']</t>
+    <t>['59', '82']</t>
+  </si>
+  <si>
+    <t>['6', '44', '90+2', '90+6']</t>
+  </si>
+  <si>
+    <t>['48', '89']</t>
+  </si>
+  <si>
+    <t>['90+1', '90+3']</t>
+  </si>
+  <si>
+    <t>['48', '68']</t>
+  </si>
+  <si>
+    <t>['60', '68']</t>
   </si>
 </sst>
 </file>
@@ -1407,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP210"/>
+  <dimension ref="A1:BP215"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1744,7 +1762,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ2">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1869,7 +1887,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -1950,7 +1968,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ3">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2153,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ4">
         <v>0.82</v>
@@ -2281,7 +2299,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2565,7 +2583,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ6">
         <v>0.18</v>
@@ -2693,7 +2711,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2774,7 +2792,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ7">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2899,7 +2917,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -2977,10 +2995,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
+        <v>1.17</v>
+      </c>
+      <c r="AQ8">
         <v>1.27</v>
-      </c>
-      <c r="AQ8">
-        <v>1.3</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3183,10 +3201,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ9">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3311,7 +3329,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3595,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ11">
         <v>1</v>
@@ -3723,7 +3741,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4959,7 +4977,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5165,7 +5183,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5861,7 +5879,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ22">
         <v>1.45</v>
@@ -5989,7 +6007,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6067,10 +6085,10 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ23">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR23">
         <v>0.86</v>
@@ -6195,7 +6213,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6276,7 +6294,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ24">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR24">
         <v>0.77</v>
@@ -6685,7 +6703,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ26">
         <v>0.18</v>
@@ -6813,7 +6831,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6894,7 +6912,7 @@
         <v>1</v>
       </c>
       <c r="AQ27">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR27">
         <v>0.83</v>
@@ -7019,7 +7037,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7097,7 +7115,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ28">
         <v>1.36</v>
@@ -7225,7 +7243,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7306,7 +7324,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ29">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR29">
         <v>1.08</v>
@@ -7509,7 +7527,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ30">
         <v>1</v>
@@ -7637,7 +7655,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7718,7 +7736,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ31">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR31">
         <v>1.62</v>
@@ -7843,7 +7861,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8255,7 +8273,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -9079,7 +9097,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9285,7 +9303,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9491,7 +9509,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9697,7 +9715,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9903,7 +9921,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -9981,7 +9999,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ42">
         <v>1.91</v>
@@ -10109,7 +10127,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10393,7 +10411,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ44">
         <v>0.7</v>
@@ -10602,7 +10620,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ45">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR45">
         <v>1.78</v>
@@ -11757,7 +11775,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -11963,7 +11981,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12041,7 +12059,7 @@
         <v>3</v>
       </c>
       <c r="AP52">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ52">
         <v>1.36</v>
@@ -12169,7 +12187,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12250,7 +12268,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ53">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR53">
         <v>1.65</v>
@@ -12456,7 +12474,7 @@
         <v>1</v>
       </c>
       <c r="AQ54">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR54">
         <v>1.48</v>
@@ -12581,7 +12599,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -12659,7 +12677,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ55">
         <v>0.5</v>
@@ -12865,7 +12883,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ56">
         <v>1.2</v>
@@ -12993,7 +13011,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13199,7 +13217,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13280,7 +13298,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ58">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR58">
         <v>1.42</v>
@@ -13405,7 +13423,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13486,7 +13504,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ59">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR59">
         <v>0.95</v>
@@ -13611,7 +13629,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13817,7 +13835,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14023,7 +14041,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14104,7 +14122,7 @@
         <v>1</v>
       </c>
       <c r="AQ62">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR62">
         <v>1.29</v>
@@ -14307,10 +14325,10 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ63">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR63">
         <v>1.12</v>
@@ -14435,7 +14453,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14516,7 +14534,7 @@
         <v>2</v>
       </c>
       <c r="AQ64">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR64">
         <v>2.4</v>
@@ -14641,7 +14659,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14719,7 +14737,7 @@
         <v>0.67</v>
       </c>
       <c r="AP65">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ65">
         <v>0.9</v>
@@ -14847,7 +14865,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14925,7 +14943,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ66">
         <v>0.82</v>
@@ -15131,7 +15149,7 @@
         <v>0</v>
       </c>
       <c r="AP67">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ67">
         <v>0.18</v>
@@ -15877,7 +15895,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16083,7 +16101,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q72">
         <v>1.95</v>
@@ -16289,7 +16307,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16370,7 +16388,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ73">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR73">
         <v>2.01</v>
@@ -16495,7 +16513,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16701,7 +16719,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16779,7 +16797,7 @@
         <v>1.33</v>
       </c>
       <c r="AP75">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ75">
         <v>1.45</v>
@@ -16907,7 +16925,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17113,7 +17131,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17525,7 +17543,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17731,7 +17749,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18018,7 +18036,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ81">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR81">
         <v>1.42</v>
@@ -18143,7 +18161,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18221,7 +18239,7 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ82">
         <v>2.09</v>
@@ -18555,7 +18573,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18761,7 +18779,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -18842,7 +18860,7 @@
         <v>2</v>
       </c>
       <c r="AQ85">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR85">
         <v>1.28</v>
@@ -18967,7 +18985,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19045,7 +19063,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ86">
         <v>0.9</v>
@@ -19254,7 +19272,7 @@
         <v>1</v>
       </c>
       <c r="AQ87">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR87">
         <v>1.26</v>
@@ -19379,7 +19397,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19791,7 +19809,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -19869,7 +19887,7 @@
         <v>1.25</v>
       </c>
       <c r="AP90">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ90">
         <v>1</v>
@@ -19997,7 +20015,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20075,10 +20093,10 @@
         <v>3</v>
       </c>
       <c r="AP91">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ91">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR91">
         <v>2.46</v>
@@ -20281,7 +20299,7 @@
         <v>1.75</v>
       </c>
       <c r="AP92">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ92">
         <v>1.73</v>
@@ -21439,7 +21457,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21520,7 +21538,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ98">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR98">
         <v>1.11</v>
@@ -21645,7 +21663,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -21726,7 +21744,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ99">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR99">
         <v>1.99</v>
@@ -21851,7 +21869,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22263,7 +22281,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22341,10 +22359,10 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ102">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR102">
         <v>1.76</v>
@@ -22469,7 +22487,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22550,7 +22568,7 @@
         <v>1</v>
       </c>
       <c r="AQ103">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR103">
         <v>1.37</v>
@@ -22753,7 +22771,7 @@
         <v>0.8</v>
       </c>
       <c r="AP104">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ104">
         <v>0.7</v>
@@ -23374,7 +23392,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ107">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR107">
         <v>1.75</v>
@@ -23705,7 +23723,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -23911,7 +23929,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24117,7 +24135,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q111">
         <v>3.25</v>
@@ -24323,7 +24341,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24401,7 +24419,7 @@
         <v>2</v>
       </c>
       <c r="AP112">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ112">
         <v>1.91</v>
@@ -24529,7 +24547,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -25019,7 +25037,7 @@
         <v>2.2</v>
       </c>
       <c r="AP115">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ115">
         <v>2.09</v>
@@ -25147,7 +25165,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25353,7 +25371,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25434,7 +25452,7 @@
         <v>2</v>
       </c>
       <c r="AQ117">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR117">
         <v>1.41</v>
@@ -25559,7 +25577,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25765,7 +25783,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -25846,7 +25864,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ119">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR119">
         <v>1.07</v>
@@ -25971,7 +25989,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26177,7 +26195,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26255,7 +26273,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ121">
         <v>1.2</v>
@@ -26383,7 +26401,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26589,7 +26607,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -26670,7 +26688,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ123">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR123">
         <v>1.13</v>
@@ -27079,7 +27097,7 @@
         <v>0.83</v>
       </c>
       <c r="AP125">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ125">
         <v>0.5</v>
@@ -27207,7 +27225,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27413,7 +27431,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -27491,7 +27509,7 @@
         <v>1.33</v>
       </c>
       <c r="AP127">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ127">
         <v>1.73</v>
@@ -27906,7 +27924,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ129">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR129">
         <v>1.64</v>
@@ -28031,7 +28049,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28112,7 +28130,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ130">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR130">
         <v>1.95</v>
@@ -28443,7 +28461,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28524,7 +28542,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ132">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR132">
         <v>1.18</v>
@@ -28727,7 +28745,7 @@
         <v>1.33</v>
       </c>
       <c r="AP133">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ133">
         <v>1.2</v>
@@ -28855,7 +28873,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29061,7 +29079,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -29139,10 +29157,10 @@
         <v>2.67</v>
       </c>
       <c r="AP135">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ135">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR135">
         <v>1.25</v>
@@ -29963,7 +29981,7 @@
         <v>1</v>
       </c>
       <c r="AP139">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ139">
         <v>1</v>
@@ -30503,7 +30521,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30709,7 +30727,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30787,7 +30805,7 @@
         <v>1.29</v>
       </c>
       <c r="AP143">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ143">
         <v>1.64</v>
@@ -31121,7 +31139,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31327,7 +31345,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31533,7 +31551,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31614,7 +31632,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ147">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR147">
         <v>1.16</v>
@@ -31739,7 +31757,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -31817,7 +31835,7 @@
         <v>1.43</v>
       </c>
       <c r="AP148">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ148">
         <v>1.45</v>
@@ -31945,7 +31963,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32229,7 +32247,7 @@
         <v>0.71</v>
       </c>
       <c r="AP150">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ150">
         <v>0.82</v>
@@ -32357,7 +32375,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -32641,7 +32659,7 @@
         <v>0.71</v>
       </c>
       <c r="AP152">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ152">
         <v>0.7</v>
@@ -32847,7 +32865,7 @@
         <v>0.71</v>
       </c>
       <c r="AP153">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ153">
         <v>0.5</v>
@@ -32975,7 +32993,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33056,7 +33074,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ154">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR154">
         <v>1.76</v>
@@ -33181,7 +33199,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33262,7 +33280,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ155">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR155">
         <v>1.52</v>
@@ -33387,7 +33405,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33468,7 +33486,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ156">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR156">
         <v>1.53</v>
@@ -33593,7 +33611,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33799,7 +33817,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34623,7 +34641,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34701,7 +34719,7 @@
         <v>1.75</v>
       </c>
       <c r="AP162">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ162">
         <v>2.09</v>
@@ -34829,7 +34847,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -34907,7 +34925,7 @@
         <v>1.38</v>
       </c>
       <c r="AP163">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ163">
         <v>1.45</v>
@@ -35035,7 +35053,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35241,7 +35259,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35653,7 +35671,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35731,7 +35749,7 @@
         <v>0.63</v>
       </c>
       <c r="AP167">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ167">
         <v>0.82</v>
@@ -35859,7 +35877,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -35940,7 +35958,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ168">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR168">
         <v>1.46</v>
@@ -36271,7 +36289,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36352,7 +36370,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ170">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR170">
         <v>1.79</v>
@@ -36683,7 +36701,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37173,10 +37191,10 @@
         <v>1.25</v>
       </c>
       <c r="AP174">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ174">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR174">
         <v>1.48</v>
@@ -37301,7 +37319,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -37382,7 +37400,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ175">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR175">
         <v>1.78</v>
@@ -37588,7 +37606,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ176">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR176">
         <v>1.74</v>
@@ -37919,7 +37937,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38409,7 +38427,7 @@
         <v>1</v>
       </c>
       <c r="AP180">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ180">
         <v>0.9</v>
@@ -38537,7 +38555,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38615,7 +38633,7 @@
         <v>1.22</v>
       </c>
       <c r="AP181">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ181">
         <v>1.36</v>
@@ -38743,7 +38761,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39155,7 +39173,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39236,7 +39254,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ184">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR184">
         <v>1.59</v>
@@ -39361,7 +39379,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39567,7 +39585,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -39645,10 +39663,10 @@
         <v>2.5</v>
       </c>
       <c r="AP186">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ186">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR186">
         <v>1.43</v>
@@ -39979,7 +39997,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40185,7 +40203,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40391,7 +40409,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40469,7 +40487,7 @@
         <v>1.67</v>
       </c>
       <c r="AP190">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ190">
         <v>1.73</v>
@@ -40597,7 +40615,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -41009,7 +41027,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41421,7 +41439,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41627,7 +41645,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -42039,7 +42057,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42245,7 +42263,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42451,7 +42469,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42657,7 +42675,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -42738,7 +42756,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ201">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR201">
         <v>1.75</v>
@@ -42863,7 +42881,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -42941,10 +42959,10 @@
         <v>1.44</v>
       </c>
       <c r="AP202">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ202">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR202">
         <v>1.35</v>
@@ -43069,7 +43087,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43147,7 +43165,7 @@
         <v>1.4</v>
       </c>
       <c r="AP203">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ203">
         <v>1.36</v>
@@ -43275,7 +43293,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43356,7 +43374,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ204">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AR204">
         <v>1.5</v>
@@ -43481,7 +43499,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -43559,10 +43577,10 @@
         <v>1.11</v>
       </c>
       <c r="AP205">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ205">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR205">
         <v>1.11</v>
@@ -43765,7 +43783,7 @@
         <v>0.9</v>
       </c>
       <c r="AP206">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ206">
         <v>0.82</v>
@@ -43893,7 +43911,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -43974,7 +43992,7 @@
         <v>1</v>
       </c>
       <c r="AQ207">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR207">
         <v>1.34</v>
@@ -44177,7 +44195,7 @@
         <v>1.11</v>
       </c>
       <c r="AP208">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ208">
         <v>1</v>
@@ -44305,7 +44323,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44668,6 +44686,1036 @@
       </c>
       <c r="BP210">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="211" spans="1:68">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7466898</v>
+      </c>
+      <c r="C211" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" t="s">
+        <v>69</v>
+      </c>
+      <c r="E211" s="2">
+        <v>45675.39583333334</v>
+      </c>
+      <c r="F211">
+        <v>22</v>
+      </c>
+      <c r="G211" t="s">
+        <v>74</v>
+      </c>
+      <c r="H211" t="s">
+        <v>88</v>
+      </c>
+      <c r="I211">
+        <v>1</v>
+      </c>
+      <c r="J211">
+        <v>2</v>
+      </c>
+      <c r="K211">
+        <v>3</v>
+      </c>
+      <c r="L211">
+        <v>1</v>
+      </c>
+      <c r="M211">
+        <v>4</v>
+      </c>
+      <c r="N211">
+        <v>5</v>
+      </c>
+      <c r="O211" t="s">
+        <v>111</v>
+      </c>
+      <c r="P211" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q211">
+        <v>2.2</v>
+      </c>
+      <c r="R211">
+        <v>2.5</v>
+      </c>
+      <c r="S211">
+        <v>4.75</v>
+      </c>
+      <c r="T211">
+        <v>1.29</v>
+      </c>
+      <c r="U211">
+        <v>3.5</v>
+      </c>
+      <c r="V211">
+        <v>2.25</v>
+      </c>
+      <c r="W211">
+        <v>1.57</v>
+      </c>
+      <c r="X211">
+        <v>5.5</v>
+      </c>
+      <c r="Y211">
+        <v>1.14</v>
+      </c>
+      <c r="Z211">
+        <v>1.79</v>
+      </c>
+      <c r="AA211">
+        <v>3.52</v>
+      </c>
+      <c r="AB211">
+        <v>3.86</v>
+      </c>
+      <c r="AC211">
+        <v>1.02</v>
+      </c>
+      <c r="AD211">
+        <v>19</v>
+      </c>
+      <c r="AE211">
+        <v>1.18</v>
+      </c>
+      <c r="AF211">
+        <v>5.1</v>
+      </c>
+      <c r="AG211">
+        <v>1.49</v>
+      </c>
+      <c r="AH211">
+        <v>2.51</v>
+      </c>
+      <c r="AI211">
+        <v>1.62</v>
+      </c>
+      <c r="AJ211">
+        <v>2.2</v>
+      </c>
+      <c r="AK211">
+        <v>1.18</v>
+      </c>
+      <c r="AL211">
+        <v>1.23</v>
+      </c>
+      <c r="AM211">
+        <v>2.2</v>
+      </c>
+      <c r="AN211">
+        <v>2</v>
+      </c>
+      <c r="AO211">
+        <v>1.45</v>
+      </c>
+      <c r="AP211">
+        <v>1.82</v>
+      </c>
+      <c r="AQ211">
+        <v>1.58</v>
+      </c>
+      <c r="AR211">
+        <v>1.61</v>
+      </c>
+      <c r="AS211">
+        <v>1.55</v>
+      </c>
+      <c r="AT211">
+        <v>3.16</v>
+      </c>
+      <c r="AU211">
+        <v>6</v>
+      </c>
+      <c r="AV211">
+        <v>11</v>
+      </c>
+      <c r="AW211">
+        <v>8</v>
+      </c>
+      <c r="AX211">
+        <v>9</v>
+      </c>
+      <c r="AY211">
+        <v>20</v>
+      </c>
+      <c r="AZ211">
+        <v>23</v>
+      </c>
+      <c r="BA211">
+        <v>7</v>
+      </c>
+      <c r="BB211">
+        <v>6</v>
+      </c>
+      <c r="BC211">
+        <v>13</v>
+      </c>
+      <c r="BD211">
+        <v>1.5</v>
+      </c>
+      <c r="BE211">
+        <v>7</v>
+      </c>
+      <c r="BF211">
+        <v>2.8</v>
+      </c>
+      <c r="BG211">
+        <v>1.13</v>
+      </c>
+      <c r="BH211">
+        <v>4.9</v>
+      </c>
+      <c r="BI211">
+        <v>1.24</v>
+      </c>
+      <c r="BJ211">
+        <v>3.55</v>
+      </c>
+      <c r="BK211">
+        <v>1.4</v>
+      </c>
+      <c r="BL211">
+        <v>2.65</v>
+      </c>
+      <c r="BM211">
+        <v>1.66</v>
+      </c>
+      <c r="BN211">
+        <v>2.07</v>
+      </c>
+      <c r="BO211">
+        <v>2</v>
+      </c>
+      <c r="BP211">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="212" spans="1:68">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>7466900</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="2">
+        <v>45675.5</v>
+      </c>
+      <c r="F212">
+        <v>22</v>
+      </c>
+      <c r="G212" t="s">
+        <v>76</v>
+      </c>
+      <c r="H212" t="s">
+        <v>82</v>
+      </c>
+      <c r="I212">
+        <v>0</v>
+      </c>
+      <c r="J212">
+        <v>0</v>
+      </c>
+      <c r="K212">
+        <v>0</v>
+      </c>
+      <c r="L212">
+        <v>0</v>
+      </c>
+      <c r="M212">
+        <v>2</v>
+      </c>
+      <c r="N212">
+        <v>2</v>
+      </c>
+      <c r="O212" t="s">
+        <v>91</v>
+      </c>
+      <c r="P212" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q212">
+        <v>3.1</v>
+      </c>
+      <c r="R212">
+        <v>2.25</v>
+      </c>
+      <c r="S212">
+        <v>3.2</v>
+      </c>
+      <c r="T212">
+        <v>1.33</v>
+      </c>
+      <c r="U212">
+        <v>3.25</v>
+      </c>
+      <c r="V212">
+        <v>2.63</v>
+      </c>
+      <c r="W212">
+        <v>1.44</v>
+      </c>
+      <c r="X212">
+        <v>7</v>
+      </c>
+      <c r="Y212">
+        <v>1.1</v>
+      </c>
+      <c r="Z212">
+        <v>2.32</v>
+      </c>
+      <c r="AA212">
+        <v>3.25</v>
+      </c>
+      <c r="AB212">
+        <v>2.76</v>
+      </c>
+      <c r="AC212">
+        <v>1.04</v>
+      </c>
+      <c r="AD212">
+        <v>14</v>
+      </c>
+      <c r="AE212">
+        <v>1.24</v>
+      </c>
+      <c r="AF212">
+        <v>4.3</v>
+      </c>
+      <c r="AG212">
+        <v>1.7</v>
+      </c>
+      <c r="AH212">
+        <v>2.08</v>
+      </c>
+      <c r="AI212">
+        <v>1.57</v>
+      </c>
+      <c r="AJ212">
+        <v>2.25</v>
+      </c>
+      <c r="AK212">
+        <v>1.43</v>
+      </c>
+      <c r="AL212">
+        <v>1.3</v>
+      </c>
+      <c r="AM212">
+        <v>1.52</v>
+      </c>
+      <c r="AN212">
+        <v>1.27</v>
+      </c>
+      <c r="AO212">
+        <v>1.3</v>
+      </c>
+      <c r="AP212">
+        <v>1.17</v>
+      </c>
+      <c r="AQ212">
+        <v>1.45</v>
+      </c>
+      <c r="AR212">
+        <v>1.29</v>
+      </c>
+      <c r="AS212">
+        <v>1.39</v>
+      </c>
+      <c r="AT212">
+        <v>2.68</v>
+      </c>
+      <c r="AU212">
+        <v>0</v>
+      </c>
+      <c r="AV212">
+        <v>8</v>
+      </c>
+      <c r="AW212">
+        <v>8</v>
+      </c>
+      <c r="AX212">
+        <v>4</v>
+      </c>
+      <c r="AY212">
+        <v>9</v>
+      </c>
+      <c r="AZ212">
+        <v>12</v>
+      </c>
+      <c r="BA212">
+        <v>2</v>
+      </c>
+      <c r="BB212">
+        <v>4</v>
+      </c>
+      <c r="BC212">
+        <v>6</v>
+      </c>
+      <c r="BD212">
+        <v>1.93</v>
+      </c>
+      <c r="BE212">
+        <v>6.75</v>
+      </c>
+      <c r="BF212">
+        <v>2.05</v>
+      </c>
+      <c r="BG212">
+        <v>1.15</v>
+      </c>
+      <c r="BH212">
+        <v>4.6</v>
+      </c>
+      <c r="BI212">
+        <v>1.27</v>
+      </c>
+      <c r="BJ212">
+        <v>3.3</v>
+      </c>
+      <c r="BK212">
+        <v>1.46</v>
+      </c>
+      <c r="BL212">
+        <v>2.48</v>
+      </c>
+      <c r="BM212">
+        <v>1.72</v>
+      </c>
+      <c r="BN212">
+        <v>1.97</v>
+      </c>
+      <c r="BO212">
+        <v>2.1</v>
+      </c>
+      <c r="BP212">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="213" spans="1:68">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>7466892</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="2">
+        <v>45675.5</v>
+      </c>
+      <c r="F213">
+        <v>22</v>
+      </c>
+      <c r="G213" t="s">
+        <v>77</v>
+      </c>
+      <c r="H213" t="s">
+        <v>89</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>0</v>
+      </c>
+      <c r="K213">
+        <v>0</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+      <c r="M213">
+        <v>2</v>
+      </c>
+      <c r="N213">
+        <v>2</v>
+      </c>
+      <c r="O213" t="s">
+        <v>91</v>
+      </c>
+      <c r="P213" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q213">
+        <v>5</v>
+      </c>
+      <c r="R213">
+        <v>2.75</v>
+      </c>
+      <c r="S213">
+        <v>1.91</v>
+      </c>
+      <c r="T213">
+        <v>1.2</v>
+      </c>
+      <c r="U213">
+        <v>4.33</v>
+      </c>
+      <c r="V213">
+        <v>1.91</v>
+      </c>
+      <c r="W213">
+        <v>1.8</v>
+      </c>
+      <c r="X213">
+        <v>4</v>
+      </c>
+      <c r="Y213">
+        <v>1.22</v>
+      </c>
+      <c r="Z213">
+        <v>5</v>
+      </c>
+      <c r="AA213">
+        <v>4.46</v>
+      </c>
+      <c r="AB213">
+        <v>1.47</v>
+      </c>
+      <c r="AC213">
+        <v>1.01</v>
+      </c>
+      <c r="AD213">
+        <v>33</v>
+      </c>
+      <c r="AE213">
+        <v>1.1</v>
+      </c>
+      <c r="AF213">
+        <v>7.6</v>
+      </c>
+      <c r="AG213">
+        <v>1.34</v>
+      </c>
+      <c r="AH213">
+        <v>3.09</v>
+      </c>
+      <c r="AI213">
+        <v>1.44</v>
+      </c>
+      <c r="AJ213">
+        <v>2.63</v>
+      </c>
+      <c r="AK213">
+        <v>2.55</v>
+      </c>
+      <c r="AL213">
+        <v>1.18</v>
+      </c>
+      <c r="AM213">
+        <v>1.14</v>
+      </c>
+      <c r="AN213">
+        <v>2.09</v>
+      </c>
+      <c r="AO213">
+        <v>2.4</v>
+      </c>
+      <c r="AP213">
+        <v>1.92</v>
+      </c>
+      <c r="AQ213">
+        <v>2.45</v>
+      </c>
+      <c r="AR213">
+        <v>1.61</v>
+      </c>
+      <c r="AS213">
+        <v>1.95</v>
+      </c>
+      <c r="AT213">
+        <v>3.56</v>
+      </c>
+      <c r="AU213">
+        <v>7</v>
+      </c>
+      <c r="AV213">
+        <v>9</v>
+      </c>
+      <c r="AW213">
+        <v>5</v>
+      </c>
+      <c r="AX213">
+        <v>29</v>
+      </c>
+      <c r="AY213">
+        <v>14</v>
+      </c>
+      <c r="AZ213">
+        <v>49</v>
+      </c>
+      <c r="BA213">
+        <v>2</v>
+      </c>
+      <c r="BB213">
+        <v>15</v>
+      </c>
+      <c r="BC213">
+        <v>17</v>
+      </c>
+      <c r="BD213">
+        <v>3.9</v>
+      </c>
+      <c r="BE213">
+        <v>8</v>
+      </c>
+      <c r="BF213">
+        <v>1.3</v>
+      </c>
+      <c r="BG213">
+        <v>1.16</v>
+      </c>
+      <c r="BH213">
+        <v>4.4</v>
+      </c>
+      <c r="BI213">
+        <v>1.29</v>
+      </c>
+      <c r="BJ213">
+        <v>3.2</v>
+      </c>
+      <c r="BK213">
+        <v>1.48</v>
+      </c>
+      <c r="BL213">
+        <v>2.43</v>
+      </c>
+      <c r="BM213">
+        <v>1.76</v>
+      </c>
+      <c r="BN213">
+        <v>1.94</v>
+      </c>
+      <c r="BO213">
+        <v>2.17</v>
+      </c>
+      <c r="BP213">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="214" spans="1:68">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>7466896</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="2">
+        <v>45675.5</v>
+      </c>
+      <c r="F214">
+        <v>22</v>
+      </c>
+      <c r="G214" t="s">
+        <v>79</v>
+      </c>
+      <c r="H214" t="s">
+        <v>83</v>
+      </c>
+      <c r="I214">
+        <v>0</v>
+      </c>
+      <c r="J214">
+        <v>0</v>
+      </c>
+      <c r="K214">
+        <v>0</v>
+      </c>
+      <c r="L214">
+        <v>0</v>
+      </c>
+      <c r="M214">
+        <v>2</v>
+      </c>
+      <c r="N214">
+        <v>2</v>
+      </c>
+      <c r="O214" t="s">
+        <v>91</v>
+      </c>
+      <c r="P214" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q214">
+        <v>4</v>
+      </c>
+      <c r="R214">
+        <v>2.3</v>
+      </c>
+      <c r="S214">
+        <v>2.5</v>
+      </c>
+      <c r="T214">
+        <v>1.33</v>
+      </c>
+      <c r="U214">
+        <v>3.25</v>
+      </c>
+      <c r="V214">
+        <v>2.5</v>
+      </c>
+      <c r="W214">
+        <v>1.5</v>
+      </c>
+      <c r="X214">
+        <v>6.5</v>
+      </c>
+      <c r="Y214">
+        <v>1.11</v>
+      </c>
+      <c r="Z214">
+        <v>3.5</v>
+      </c>
+      <c r="AA214">
+        <v>3.41</v>
+      </c>
+      <c r="AB214">
+        <v>1.83</v>
+      </c>
+      <c r="AC214">
+        <v>1.04</v>
+      </c>
+      <c r="AD214">
+        <v>15</v>
+      </c>
+      <c r="AE214">
+        <v>1.24</v>
+      </c>
+      <c r="AF214">
+        <v>4.25</v>
+      </c>
+      <c r="AG214">
+        <v>1.67</v>
+      </c>
+      <c r="AH214">
+        <v>2.12</v>
+      </c>
+      <c r="AI214">
+        <v>1.62</v>
+      </c>
+      <c r="AJ214">
+        <v>2.2</v>
+      </c>
+      <c r="AK214">
+        <v>1.85</v>
+      </c>
+      <c r="AL214">
+        <v>1.27</v>
+      </c>
+      <c r="AM214">
+        <v>1.25</v>
+      </c>
+      <c r="AN214">
+        <v>0.82</v>
+      </c>
+      <c r="AO214">
+        <v>1.3</v>
+      </c>
+      <c r="AP214">
+        <v>0.75</v>
+      </c>
+      <c r="AQ214">
+        <v>1.45</v>
+      </c>
+      <c r="AR214">
+        <v>1.2</v>
+      </c>
+      <c r="AS214">
+        <v>1.45</v>
+      </c>
+      <c r="AT214">
+        <v>2.65</v>
+      </c>
+      <c r="AU214">
+        <v>5</v>
+      </c>
+      <c r="AV214">
+        <v>3</v>
+      </c>
+      <c r="AW214">
+        <v>4</v>
+      </c>
+      <c r="AX214">
+        <v>15</v>
+      </c>
+      <c r="AY214">
+        <v>10</v>
+      </c>
+      <c r="AZ214">
+        <v>24</v>
+      </c>
+      <c r="BA214">
+        <v>5</v>
+      </c>
+      <c r="BB214">
+        <v>2</v>
+      </c>
+      <c r="BC214">
+        <v>7</v>
+      </c>
+      <c r="BD214">
+        <v>2.7</v>
+      </c>
+      <c r="BE214">
+        <v>6.75</v>
+      </c>
+      <c r="BF214">
+        <v>1.54</v>
+      </c>
+      <c r="BG214">
+        <v>1.23</v>
+      </c>
+      <c r="BH214">
+        <v>3.65</v>
+      </c>
+      <c r="BI214">
+        <v>1.41</v>
+      </c>
+      <c r="BJ214">
+        <v>2.65</v>
+      </c>
+      <c r="BK214">
+        <v>1.66</v>
+      </c>
+      <c r="BL214">
+        <v>2.06</v>
+      </c>
+      <c r="BM214">
+        <v>2.05</v>
+      </c>
+      <c r="BN214">
+        <v>1.67</v>
+      </c>
+      <c r="BO214">
+        <v>2.55</v>
+      </c>
+      <c r="BP214">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="215" spans="1:68">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7466891</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="2">
+        <v>45675.60416666666</v>
+      </c>
+      <c r="F215">
+        <v>22</v>
+      </c>
+      <c r="G215" t="s">
+        <v>72</v>
+      </c>
+      <c r="H215" t="s">
+        <v>86</v>
+      </c>
+      <c r="I215">
+        <v>1</v>
+      </c>
+      <c r="J215">
+        <v>0</v>
+      </c>
+      <c r="K215">
+        <v>1</v>
+      </c>
+      <c r="L215">
+        <v>2</v>
+      </c>
+      <c r="M215">
+        <v>2</v>
+      </c>
+      <c r="N215">
+        <v>4</v>
+      </c>
+      <c r="O215" t="s">
+        <v>237</v>
+      </c>
+      <c r="P215" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q215">
+        <v>2</v>
+      </c>
+      <c r="R215">
+        <v>2.4</v>
+      </c>
+      <c r="S215">
+        <v>6</v>
+      </c>
+      <c r="T215">
+        <v>1.33</v>
+      </c>
+      <c r="U215">
+        <v>3.25</v>
+      </c>
+      <c r="V215">
+        <v>2.63</v>
+      </c>
+      <c r="W215">
+        <v>1.44</v>
+      </c>
+      <c r="X215">
+        <v>6.5</v>
+      </c>
+      <c r="Y215">
+        <v>1.11</v>
+      </c>
+      <c r="Z215">
+        <v>1.5</v>
+      </c>
+      <c r="AA215">
+        <v>4.3</v>
+      </c>
+      <c r="AB215">
+        <v>6.5</v>
+      </c>
+      <c r="AC215">
+        <v>1.03</v>
+      </c>
+      <c r="AD215">
+        <v>16</v>
+      </c>
+      <c r="AE215">
+        <v>1.24</v>
+      </c>
+      <c r="AF215">
+        <v>4.25</v>
+      </c>
+      <c r="AG215">
+        <v>1.67</v>
+      </c>
+      <c r="AH215">
+        <v>2.17</v>
+      </c>
+      <c r="AI215">
+        <v>1.91</v>
+      </c>
+      <c r="AJ215">
+        <v>1.91</v>
+      </c>
+      <c r="AK215">
+        <v>1.11</v>
+      </c>
+      <c r="AL215">
+        <v>1.2</v>
+      </c>
+      <c r="AM215">
+        <v>2.65</v>
+      </c>
+      <c r="AN215">
+        <v>2.4</v>
+      </c>
+      <c r="AO215">
+        <v>1.3</v>
+      </c>
+      <c r="AP215">
+        <v>2.27</v>
+      </c>
+      <c r="AQ215">
+        <v>1.27</v>
+      </c>
+      <c r="AR215">
+        <v>1.97</v>
+      </c>
+      <c r="AS215">
+        <v>1.14</v>
+      </c>
+      <c r="AT215">
+        <v>3.11</v>
+      </c>
+      <c r="AU215">
+        <v>6</v>
+      </c>
+      <c r="AV215">
+        <v>5</v>
+      </c>
+      <c r="AW215">
+        <v>12</v>
+      </c>
+      <c r="AX215">
+        <v>4</v>
+      </c>
+      <c r="AY215">
+        <v>22</v>
+      </c>
+      <c r="AZ215">
+        <v>10</v>
+      </c>
+      <c r="BA215">
+        <v>10</v>
+      </c>
+      <c r="BB215">
+        <v>1</v>
+      </c>
+      <c r="BC215">
+        <v>11</v>
+      </c>
+      <c r="BD215">
+        <v>1.32</v>
+      </c>
+      <c r="BE215">
+        <v>7.5</v>
+      </c>
+      <c r="BF215">
+        <v>3.65</v>
+      </c>
+      <c r="BG215">
+        <v>1.27</v>
+      </c>
+      <c r="BH215">
+        <v>3.3</v>
+      </c>
+      <c r="BI215">
+        <v>1.48</v>
+      </c>
+      <c r="BJ215">
+        <v>2.43</v>
+      </c>
+      <c r="BK215">
+        <v>1.78</v>
+      </c>
+      <c r="BL215">
+        <v>1.91</v>
+      </c>
+      <c r="BM215">
+        <v>2.2</v>
+      </c>
+      <c r="BN215">
+        <v>1.57</v>
+      </c>
+      <c r="BO215">
+        <v>2.8</v>
+      </c>
+      <c r="BP215">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="356">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -730,6 +730,12 @@
     <t>['35', '55']</t>
   </si>
   <si>
+    <t>['11', '28', '41']</t>
+  </si>
+  <si>
+    <t>['13', '30', '45+7']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1064,6 +1070,18 @@
   </si>
   <si>
     <t>['60', '68']</t>
+  </si>
+  <si>
+    <t>['5', '60', '76']</t>
+  </si>
+  <si>
+    <t>['60', '90+1']</t>
+  </si>
+  <si>
+    <t>['77', '90+2']</t>
+  </si>
+  <si>
+    <t>['27', '30', '42', '49', '57', '69']</t>
   </si>
 </sst>
 </file>
@@ -1425,7 +1443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP215"/>
+  <dimension ref="A1:BP219"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1759,7 +1777,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ2">
         <v>1.45</v>
@@ -1887,7 +1905,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -1965,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ3">
         <v>2.45</v>
@@ -2299,7 +2317,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2377,10 +2395,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ5">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2586,7 +2604,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ6">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2711,7 +2729,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2789,7 +2807,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ7">
         <v>1.58</v>
@@ -2917,7 +2935,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3329,7 +3347,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3410,7 +3428,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ10">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3616,7 +3634,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ11">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3741,7 +3759,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4977,7 +4995,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5183,7 +5201,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5882,7 +5900,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ22">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR22">
         <v>1.72</v>
@@ -6007,7 +6025,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6213,7 +6231,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6291,7 +6309,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ24">
         <v>1.45</v>
@@ -6497,7 +6515,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ25">
         <v>0.82</v>
@@ -6706,7 +6724,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ26">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR26">
         <v>1.29</v>
@@ -6831,7 +6849,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6909,7 +6927,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ27">
         <v>1.58</v>
@@ -7037,7 +7055,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7118,7 +7136,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ28">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR28">
         <v>1.25</v>
@@ -7243,7 +7261,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7530,7 +7548,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR30">
         <v>0.47</v>
@@ -7655,7 +7673,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7733,7 +7751,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ31">
         <v>2.45</v>
@@ -7861,7 +7879,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8273,7 +8291,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -9097,7 +9115,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9303,7 +9321,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9509,7 +9527,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9715,7 +9733,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9921,7 +9939,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10127,7 +10145,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -11775,7 +11793,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -11981,7 +11999,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12062,7 +12080,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ52">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR52">
         <v>0.75</v>
@@ -12187,7 +12205,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12265,7 +12283,7 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ53">
         <v>1.45</v>
@@ -12471,7 +12489,7 @@
         <v>0.5</v>
       </c>
       <c r="AP54">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ54">
         <v>1.45</v>
@@ -12599,7 +12617,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -13011,7 +13029,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13092,7 +13110,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ57">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR57">
         <v>1.39</v>
@@ -13217,7 +13235,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13423,7 +13441,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13501,7 +13519,7 @@
         <v>3</v>
       </c>
       <c r="AP59">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ59">
         <v>1.27</v>
@@ -13629,7 +13647,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13707,10 +13725,10 @@
         <v>0.5</v>
       </c>
       <c r="AP60">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ60">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR60">
         <v>1.43</v>
@@ -13835,7 +13853,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -13916,7 +13934,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ61">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR61">
         <v>1.76</v>
@@ -14041,7 +14059,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14453,7 +14471,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14659,7 +14677,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14865,7 +14883,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -15152,7 +15170,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ67">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR67">
         <v>2.4</v>
@@ -15355,7 +15373,7 @@
         <v>1.33</v>
       </c>
       <c r="AP68">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ68">
         <v>1.64</v>
@@ -15895,7 +15913,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -15976,7 +15994,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ71">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR71">
         <v>1.59</v>
@@ -16101,7 +16119,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q72">
         <v>1.95</v>
@@ -16307,7 +16325,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16513,7 +16531,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16591,7 +16609,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ74">
         <v>0.5</v>
@@ -16719,7 +16737,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16800,7 +16818,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ75">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR75">
         <v>0.91</v>
@@ -16925,7 +16943,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17131,7 +17149,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17209,7 +17227,7 @@
         <v>0.33</v>
       </c>
       <c r="AP77">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ77">
         <v>0.7</v>
@@ -17543,7 +17561,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17624,7 +17642,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ79">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR79">
         <v>1.27</v>
@@ -17749,7 +17767,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18033,7 +18051,7 @@
         <v>0.33</v>
       </c>
       <c r="AP81">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ81">
         <v>1.45</v>
@@ -18161,7 +18179,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18448,7 +18466,7 @@
         <v>2</v>
       </c>
       <c r="AQ83">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR83">
         <v>2.31</v>
@@ -18573,7 +18591,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18779,7 +18797,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -18985,7 +19003,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19269,7 +19287,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ87">
         <v>1.45</v>
@@ -19397,7 +19415,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19684,7 +19702,7 @@
         <v>1</v>
       </c>
       <c r="AQ89">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR89">
         <v>1.28</v>
@@ -19809,7 +19827,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20015,7 +20033,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20714,7 +20732,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ94">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR94">
         <v>1.6</v>
@@ -20917,7 +20935,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ95">
         <v>0.5</v>
@@ -21126,7 +21144,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ96">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR96">
         <v>1.78</v>
@@ -21329,7 +21347,7 @@
         <v>1.25</v>
       </c>
       <c r="AP97">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ97">
         <v>1.2</v>
@@ -21457,7 +21475,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21663,7 +21681,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -21869,7 +21887,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -21947,7 +21965,7 @@
         <v>2.25</v>
       </c>
       <c r="AP100">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ100">
         <v>1.91</v>
@@ -22281,7 +22299,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22487,7 +22505,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22980,7 +22998,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ105">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR105">
         <v>1.17</v>
@@ -23186,7 +23204,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ106">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR106">
         <v>1.54</v>
@@ -23595,7 +23613,7 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ108">
         <v>0.5</v>
@@ -23723,7 +23741,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -23801,7 +23819,7 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ109">
         <v>1.64</v>
@@ -23929,7 +23947,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24135,7 +24153,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q111">
         <v>3.25</v>
@@ -24341,7 +24359,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24547,7 +24565,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24831,7 +24849,7 @@
         <v>0</v>
       </c>
       <c r="AP114">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ114">
         <v>0.5</v>
@@ -25165,7 +25183,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25246,7 +25264,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ116">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR116">
         <v>1.57</v>
@@ -25371,7 +25389,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25577,7 +25595,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25658,7 +25676,7 @@
         <v>2</v>
       </c>
       <c r="AQ118">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR118">
         <v>2.34</v>
@@ -25783,7 +25801,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -25989,7 +26007,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26067,7 +26085,7 @@
         <v>1</v>
       </c>
       <c r="AP120">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ120">
         <v>1</v>
@@ -26195,7 +26213,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26401,7 +26419,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26482,7 +26500,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ122">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR122">
         <v>1.46</v>
@@ -26607,7 +26625,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -26891,7 +26909,7 @@
         <v>0.83</v>
       </c>
       <c r="AP124">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ124">
         <v>0.9</v>
@@ -27225,7 +27243,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27431,7 +27449,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -27715,7 +27733,7 @@
         <v>0.83</v>
       </c>
       <c r="AP128">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ128">
         <v>0.7</v>
@@ -28049,7 +28067,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28336,7 +28354,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ131">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR131">
         <v>1.72</v>
@@ -28461,7 +28479,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28539,7 +28557,7 @@
         <v>0.5</v>
       </c>
       <c r="AP132">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ132">
         <v>1.45</v>
@@ -28873,7 +28891,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29079,7 +29097,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -29569,7 +29587,7 @@
         <v>0.83</v>
       </c>
       <c r="AP137">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ137">
         <v>0.82</v>
@@ -30190,7 +30208,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ140">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR140">
         <v>1.88</v>
@@ -30396,7 +30414,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ141">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR141">
         <v>1.64</v>
@@ -30521,7 +30539,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30602,7 +30620,7 @@
         <v>1</v>
       </c>
       <c r="AQ142">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR142">
         <v>1.38</v>
@@ -30727,7 +30745,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -31014,7 +31032,7 @@
         <v>2</v>
       </c>
       <c r="AQ144">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR144">
         <v>1.54</v>
@@ -31139,7 +31157,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31217,7 +31235,7 @@
         <v>1.57</v>
       </c>
       <c r="AP145">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ145">
         <v>2.09</v>
@@ -31345,7 +31363,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31551,7 +31569,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31629,7 +31647,7 @@
         <v>1.14</v>
       </c>
       <c r="AP147">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ147">
         <v>1.58</v>
@@ -31757,7 +31775,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -31838,7 +31856,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ148">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR148">
         <v>1.08</v>
@@ -31963,7 +31981,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32375,7 +32393,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -32993,7 +33011,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33199,7 +33217,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33277,7 +33295,7 @@
         <v>1.43</v>
       </c>
       <c r="AP155">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ155">
         <v>1.27</v>
@@ -33405,7 +33423,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33611,7 +33629,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33817,7 +33835,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -33898,7 +33916,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ158">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR158">
         <v>1.06</v>
@@ -34516,7 +34534,7 @@
         <v>2</v>
       </c>
       <c r="AQ161">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR161">
         <v>1.54</v>
@@ -34641,7 +34659,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34847,7 +34865,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -34928,7 +34946,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ163">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR163">
         <v>1.48</v>
@@ -35053,7 +35071,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35131,7 +35149,7 @@
         <v>1.13</v>
       </c>
       <c r="AP164">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ164">
         <v>1.64</v>
@@ -35259,7 +35277,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35546,7 +35564,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ166">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR166">
         <v>1.59</v>
@@ -35671,7 +35689,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35877,7 +35895,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -35955,7 +35973,7 @@
         <v>1.38</v>
       </c>
       <c r="AP168">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ168">
         <v>1.58</v>
@@ -36161,7 +36179,7 @@
         <v>2.38</v>
       </c>
       <c r="AP169">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ169">
         <v>1.91</v>
@@ -36289,7 +36307,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36701,7 +36719,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -36985,10 +37003,10 @@
         <v>1.25</v>
       </c>
       <c r="AP173">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ173">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR173">
         <v>1.56</v>
@@ -37319,7 +37337,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -37937,7 +37955,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38555,7 +38573,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38636,7 +38654,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ181">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR181">
         <v>1.08</v>
@@ -38761,7 +38779,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39048,7 +39066,7 @@
         <v>1</v>
       </c>
       <c r="AQ183">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR183">
         <v>1.34</v>
@@ -39173,7 +39191,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39379,7 +39397,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39457,7 +39475,7 @@
         <v>1.89</v>
       </c>
       <c r="AP185">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ185">
         <v>2.09</v>
@@ -39585,7 +39603,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -39869,7 +39887,7 @@
         <v>2.22</v>
       </c>
       <c r="AP187">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ187">
         <v>1.91</v>
@@ -39997,7 +40015,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40078,7 +40096,7 @@
         <v>2</v>
       </c>
       <c r="AQ188">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR188">
         <v>1.51</v>
@@ -40203,7 +40221,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40281,7 +40299,7 @@
         <v>1.33</v>
       </c>
       <c r="AP189">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ189">
         <v>1.64</v>
@@ -40409,7 +40427,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40615,7 +40633,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -41027,7 +41045,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41439,7 +41457,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41645,7 +41663,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -42057,7 +42075,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42263,7 +42281,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42469,7 +42487,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42675,7 +42693,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -42881,7 +42899,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43087,7 +43105,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43168,7 +43186,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ203">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR203">
         <v>1.57</v>
@@ -43293,7 +43311,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43371,7 +43389,7 @@
         <v>2.56</v>
       </c>
       <c r="AP204">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ204">
         <v>2.45</v>
@@ -43499,7 +43517,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -43911,7 +43929,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -43989,7 +44007,7 @@
         <v>1.11</v>
       </c>
       <c r="AP207">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ207">
         <v>1.27</v>
@@ -44198,7 +44216,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ208">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR208">
         <v>1.98</v>
@@ -44323,7 +44341,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44401,10 +44419,10 @@
         <v>1.3</v>
       </c>
       <c r="AP209">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ209">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR209">
         <v>1.16</v>
@@ -44607,10 +44625,10 @@
         <v>0.2</v>
       </c>
       <c r="AP210">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ210">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR210">
         <v>1.48</v>
@@ -44735,7 +44753,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -44941,7 +44959,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45147,7 +45165,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45353,7 +45371,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45559,7 +45577,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -45716,6 +45734,830 @@
       </c>
       <c r="BP215">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="216" spans="1:68">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>7466897</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="2">
+        <v>45676.45833333334</v>
+      </c>
+      <c r="F216">
+        <v>22</v>
+      </c>
+      <c r="G216" t="s">
+        <v>70</v>
+      </c>
+      <c r="H216" t="s">
+        <v>80</v>
+      </c>
+      <c r="I216">
+        <v>1</v>
+      </c>
+      <c r="J216">
+        <v>1</v>
+      </c>
+      <c r="K216">
+        <v>2</v>
+      </c>
+      <c r="L216">
+        <v>1</v>
+      </c>
+      <c r="M216">
+        <v>3</v>
+      </c>
+      <c r="N216">
+        <v>4</v>
+      </c>
+      <c r="O216" t="s">
+        <v>94</v>
+      </c>
+      <c r="P216" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q216">
+        <v>2.63</v>
+      </c>
+      <c r="R216">
+        <v>2.3</v>
+      </c>
+      <c r="S216">
+        <v>3.75</v>
+      </c>
+      <c r="T216">
+        <v>1.33</v>
+      </c>
+      <c r="U216">
+        <v>3.25</v>
+      </c>
+      <c r="V216">
+        <v>2.5</v>
+      </c>
+      <c r="W216">
+        <v>1.5</v>
+      </c>
+      <c r="X216">
+        <v>6.5</v>
+      </c>
+      <c r="Y216">
+        <v>1.11</v>
+      </c>
+      <c r="Z216">
+        <v>2</v>
+      </c>
+      <c r="AA216">
+        <v>3.6</v>
+      </c>
+      <c r="AB216">
+        <v>3.4</v>
+      </c>
+      <c r="AC216">
+        <v>1.04</v>
+      </c>
+      <c r="AD216">
+        <v>14</v>
+      </c>
+      <c r="AE216">
+        <v>1.24</v>
+      </c>
+      <c r="AF216">
+        <v>4.25</v>
+      </c>
+      <c r="AG216">
+        <v>1.67</v>
+      </c>
+      <c r="AH216">
+        <v>2.2</v>
+      </c>
+      <c r="AI216">
+        <v>1.62</v>
+      </c>
+      <c r="AJ216">
+        <v>2.2</v>
+      </c>
+      <c r="AK216">
+        <v>1.31</v>
+      </c>
+      <c r="AL216">
+        <v>1.28</v>
+      </c>
+      <c r="AM216">
+        <v>1.75</v>
+      </c>
+      <c r="AN216">
+        <v>1.45</v>
+      </c>
+      <c r="AO216">
+        <v>1.45</v>
+      </c>
+      <c r="AP216">
+        <v>1.33</v>
+      </c>
+      <c r="AQ216">
+        <v>1.58</v>
+      </c>
+      <c r="AR216">
+        <v>1.58</v>
+      </c>
+      <c r="AS216">
+        <v>1.41</v>
+      </c>
+      <c r="AT216">
+        <v>2.99</v>
+      </c>
+      <c r="AU216">
+        <v>2</v>
+      </c>
+      <c r="AV216">
+        <v>4</v>
+      </c>
+      <c r="AW216">
+        <v>3</v>
+      </c>
+      <c r="AX216">
+        <v>1</v>
+      </c>
+      <c r="AY216">
+        <v>11</v>
+      </c>
+      <c r="AZ216">
+        <v>7</v>
+      </c>
+      <c r="BA216">
+        <v>4</v>
+      </c>
+      <c r="BB216">
+        <v>2</v>
+      </c>
+      <c r="BC216">
+        <v>6</v>
+      </c>
+      <c r="BD216">
+        <v>1.67</v>
+      </c>
+      <c r="BE216">
+        <v>6.75</v>
+      </c>
+      <c r="BF216">
+        <v>2.43</v>
+      </c>
+      <c r="BG216">
+        <v>1.21</v>
+      </c>
+      <c r="BH216">
+        <v>3.8</v>
+      </c>
+      <c r="BI216">
+        <v>1.38</v>
+      </c>
+      <c r="BJ216">
+        <v>2.7</v>
+      </c>
+      <c r="BK216">
+        <v>1.64</v>
+      </c>
+      <c r="BL216">
+        <v>2.1</v>
+      </c>
+      <c r="BM216">
+        <v>1.98</v>
+      </c>
+      <c r="BN216">
+        <v>1.72</v>
+      </c>
+      <c r="BO216">
+        <v>2.5</v>
+      </c>
+      <c r="BP216">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="217" spans="1:68">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>7466899</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="2">
+        <v>45676.45833333334</v>
+      </c>
+      <c r="F217">
+        <v>22</v>
+      </c>
+      <c r="G217" t="s">
+        <v>75</v>
+      </c>
+      <c r="H217" t="s">
+        <v>84</v>
+      </c>
+      <c r="I217">
+        <v>3</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>3</v>
+      </c>
+      <c r="L217">
+        <v>3</v>
+      </c>
+      <c r="M217">
+        <v>2</v>
+      </c>
+      <c r="N217">
+        <v>5</v>
+      </c>
+      <c r="O217" t="s">
+        <v>238</v>
+      </c>
+      <c r="P217" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q217">
+        <v>1.95</v>
+      </c>
+      <c r="R217">
+        <v>2.38</v>
+      </c>
+      <c r="S217">
+        <v>7</v>
+      </c>
+      <c r="T217">
+        <v>1.36</v>
+      </c>
+      <c r="U217">
+        <v>3</v>
+      </c>
+      <c r="V217">
+        <v>2.63</v>
+      </c>
+      <c r="W217">
+        <v>1.44</v>
+      </c>
+      <c r="X217">
+        <v>7</v>
+      </c>
+      <c r="Y217">
+        <v>1.1</v>
+      </c>
+      <c r="Z217">
+        <v>1.38</v>
+      </c>
+      <c r="AA217">
+        <v>5</v>
+      </c>
+      <c r="AB217">
+        <v>8.31</v>
+      </c>
+      <c r="AC217">
+        <v>1.04</v>
+      </c>
+      <c r="AD217">
+        <v>14</v>
+      </c>
+      <c r="AE217">
+        <v>1.27</v>
+      </c>
+      <c r="AF217">
+        <v>4</v>
+      </c>
+      <c r="AG217">
+        <v>1.68</v>
+      </c>
+      <c r="AH217">
+        <v>2.11</v>
+      </c>
+      <c r="AI217">
+        <v>2</v>
+      </c>
+      <c r="AJ217">
+        <v>1.75</v>
+      </c>
+      <c r="AK217">
+        <v>1.11</v>
+      </c>
+      <c r="AL217">
+        <v>1.2</v>
+      </c>
+      <c r="AM217">
+        <v>2.65</v>
+      </c>
+      <c r="AN217">
+        <v>1.8</v>
+      </c>
+      <c r="AO217">
+        <v>0.18</v>
+      </c>
+      <c r="AP217">
+        <v>1.91</v>
+      </c>
+      <c r="AQ217">
+        <v>0.17</v>
+      </c>
+      <c r="AR217">
+        <v>1.44</v>
+      </c>
+      <c r="AS217">
+        <v>1.01</v>
+      </c>
+      <c r="AT217">
+        <v>2.45</v>
+      </c>
+      <c r="AU217">
+        <v>6</v>
+      </c>
+      <c r="AV217">
+        <v>5</v>
+      </c>
+      <c r="AW217">
+        <v>9</v>
+      </c>
+      <c r="AX217">
+        <v>6</v>
+      </c>
+      <c r="AY217">
+        <v>18</v>
+      </c>
+      <c r="AZ217">
+        <v>15</v>
+      </c>
+      <c r="BA217">
+        <v>2</v>
+      </c>
+      <c r="BB217">
+        <v>8</v>
+      </c>
+      <c r="BC217">
+        <v>10</v>
+      </c>
+      <c r="BD217">
+        <v>1.38</v>
+      </c>
+      <c r="BE217">
+        <v>7.5</v>
+      </c>
+      <c r="BF217">
+        <v>3.4</v>
+      </c>
+      <c r="BG217">
+        <v>1.18</v>
+      </c>
+      <c r="BH217">
+        <v>4.1</v>
+      </c>
+      <c r="BI217">
+        <v>1.32</v>
+      </c>
+      <c r="BJ217">
+        <v>3.05</v>
+      </c>
+      <c r="BK217">
+        <v>1.54</v>
+      </c>
+      <c r="BL217">
+        <v>2.3</v>
+      </c>
+      <c r="BM217">
+        <v>1.85</v>
+      </c>
+      <c r="BN217">
+        <v>1.83</v>
+      </c>
+      <c r="BO217">
+        <v>2.32</v>
+      </c>
+      <c r="BP217">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="218" spans="1:68">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>7466894</v>
+      </c>
+      <c r="C218" t="s">
+        <v>68</v>
+      </c>
+      <c r="D218" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="2">
+        <v>45676.45833333334</v>
+      </c>
+      <c r="F218">
+        <v>22</v>
+      </c>
+      <c r="G218" t="s">
+        <v>73</v>
+      </c>
+      <c r="H218" t="s">
+        <v>81</v>
+      </c>
+      <c r="I218">
+        <v>3</v>
+      </c>
+      <c r="J218">
+        <v>0</v>
+      </c>
+      <c r="K218">
+        <v>3</v>
+      </c>
+      <c r="L218">
+        <v>3</v>
+      </c>
+      <c r="M218">
+        <v>2</v>
+      </c>
+      <c r="N218">
+        <v>5</v>
+      </c>
+      <c r="O218" t="s">
+        <v>239</v>
+      </c>
+      <c r="P218" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q218">
+        <v>3.25</v>
+      </c>
+      <c r="R218">
+        <v>2.3</v>
+      </c>
+      <c r="S218">
+        <v>3</v>
+      </c>
+      <c r="T218">
+        <v>1.33</v>
+      </c>
+      <c r="U218">
+        <v>3.25</v>
+      </c>
+      <c r="V218">
+        <v>2.5</v>
+      </c>
+      <c r="W218">
+        <v>1.5</v>
+      </c>
+      <c r="X218">
+        <v>6.5</v>
+      </c>
+      <c r="Y218">
+        <v>1.11</v>
+      </c>
+      <c r="Z218">
+        <v>2.99</v>
+      </c>
+      <c r="AA218">
+        <v>3.45</v>
+      </c>
+      <c r="AB218">
+        <v>2.38</v>
+      </c>
+      <c r="AC218">
+        <v>1.04</v>
+      </c>
+      <c r="AD218">
+        <v>14</v>
+      </c>
+      <c r="AE218">
+        <v>1.23</v>
+      </c>
+      <c r="AF218">
+        <v>4.45</v>
+      </c>
+      <c r="AG218">
+        <v>1.62</v>
+      </c>
+      <c r="AH218">
+        <v>2.21</v>
+      </c>
+      <c r="AI218">
+        <v>1.53</v>
+      </c>
+      <c r="AJ218">
+        <v>2.38</v>
+      </c>
+      <c r="AK218">
+        <v>1.53</v>
+      </c>
+      <c r="AL218">
+        <v>1.29</v>
+      </c>
+      <c r="AM218">
+        <v>1.44</v>
+      </c>
+      <c r="AN218">
+        <v>1</v>
+      </c>
+      <c r="AO218">
+        <v>1</v>
+      </c>
+      <c r="AP218">
+        <v>1.18</v>
+      </c>
+      <c r="AQ218">
+        <v>0.91</v>
+      </c>
+      <c r="AR218">
+        <v>1.33</v>
+      </c>
+      <c r="AS218">
+        <v>1.62</v>
+      </c>
+      <c r="AT218">
+        <v>2.95</v>
+      </c>
+      <c r="AU218">
+        <v>7</v>
+      </c>
+      <c r="AV218">
+        <v>7</v>
+      </c>
+      <c r="AW218">
+        <v>6</v>
+      </c>
+      <c r="AX218">
+        <v>5</v>
+      </c>
+      <c r="AY218">
+        <v>15</v>
+      </c>
+      <c r="AZ218">
+        <v>16</v>
+      </c>
+      <c r="BA218">
+        <v>3</v>
+      </c>
+      <c r="BB218">
+        <v>8</v>
+      </c>
+      <c r="BC218">
+        <v>11</v>
+      </c>
+      <c r="BD218">
+        <v>2.18</v>
+      </c>
+      <c r="BE218">
+        <v>7</v>
+      </c>
+      <c r="BF218">
+        <v>1.77</v>
+      </c>
+      <c r="BG218">
+        <v>1.13</v>
+      </c>
+      <c r="BH218">
+        <v>4.9</v>
+      </c>
+      <c r="BI218">
+        <v>1.24</v>
+      </c>
+      <c r="BJ218">
+        <v>3.55</v>
+      </c>
+      <c r="BK218">
+        <v>1.41</v>
+      </c>
+      <c r="BL218">
+        <v>2.65</v>
+      </c>
+      <c r="BM218">
+        <v>1.65</v>
+      </c>
+      <c r="BN218">
+        <v>2.08</v>
+      </c>
+      <c r="BO218">
+        <v>1.98</v>
+      </c>
+      <c r="BP218">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="219" spans="1:68">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>7466895</v>
+      </c>
+      <c r="C219" t="s">
+        <v>68</v>
+      </c>
+      <c r="D219" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="2">
+        <v>45676.5625</v>
+      </c>
+      <c r="F219">
+        <v>22</v>
+      </c>
+      <c r="G219" t="s">
+        <v>71</v>
+      </c>
+      <c r="H219" t="s">
+        <v>85</v>
+      </c>
+      <c r="I219">
+        <v>0</v>
+      </c>
+      <c r="J219">
+        <v>3</v>
+      </c>
+      <c r="K219">
+        <v>3</v>
+      </c>
+      <c r="L219">
+        <v>0</v>
+      </c>
+      <c r="M219">
+        <v>6</v>
+      </c>
+      <c r="N219">
+        <v>6</v>
+      </c>
+      <c r="O219" t="s">
+        <v>91</v>
+      </c>
+      <c r="P219" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q219">
+        <v>7</v>
+      </c>
+      <c r="R219">
+        <v>2.75</v>
+      </c>
+      <c r="S219">
+        <v>1.8</v>
+      </c>
+      <c r="T219">
+        <v>1.22</v>
+      </c>
+      <c r="U219">
+        <v>4</v>
+      </c>
+      <c r="V219">
+        <v>2.1</v>
+      </c>
+      <c r="W219">
+        <v>1.67</v>
+      </c>
+      <c r="X219">
+        <v>4.5</v>
+      </c>
+      <c r="Y219">
+        <v>1.18</v>
+      </c>
+      <c r="Z219">
+        <v>8</v>
+      </c>
+      <c r="AA219">
+        <v>5</v>
+      </c>
+      <c r="AB219">
+        <v>1.33</v>
+      </c>
+      <c r="AC219">
+        <v>1.01</v>
+      </c>
+      <c r="AD219">
+        <v>25</v>
+      </c>
+      <c r="AE219">
+        <v>1.13</v>
+      </c>
+      <c r="AF219">
+        <v>6.4</v>
+      </c>
+      <c r="AG219">
+        <v>1.44</v>
+      </c>
+      <c r="AH219">
+        <v>2.75</v>
+      </c>
+      <c r="AI219">
+        <v>1.7</v>
+      </c>
+      <c r="AJ219">
+        <v>2.05</v>
+      </c>
+      <c r="AK219">
+        <v>3.25</v>
+      </c>
+      <c r="AL219">
+        <v>1.14</v>
+      </c>
+      <c r="AM219">
+        <v>1.08</v>
+      </c>
+      <c r="AN219">
+        <v>0.64</v>
+      </c>
+      <c r="AO219">
+        <v>1.36</v>
+      </c>
+      <c r="AP219">
+        <v>0.58</v>
+      </c>
+      <c r="AQ219">
+        <v>1.5</v>
+      </c>
+      <c r="AR219">
+        <v>1.13</v>
+      </c>
+      <c r="AS219">
+        <v>1.86</v>
+      </c>
+      <c r="AT219">
+        <v>2.99</v>
+      </c>
+      <c r="AU219">
+        <v>5</v>
+      </c>
+      <c r="AV219">
+        <v>10</v>
+      </c>
+      <c r="AW219">
+        <v>4</v>
+      </c>
+      <c r="AX219">
+        <v>8</v>
+      </c>
+      <c r="AY219">
+        <v>11</v>
+      </c>
+      <c r="AZ219">
+        <v>22</v>
+      </c>
+      <c r="BA219">
+        <v>4</v>
+      </c>
+      <c r="BB219">
+        <v>7</v>
+      </c>
+      <c r="BC219">
+        <v>11</v>
+      </c>
+      <c r="BD219">
+        <v>5.1</v>
+      </c>
+      <c r="BE219">
+        <v>9</v>
+      </c>
+      <c r="BF219">
+        <v>1.18</v>
+      </c>
+      <c r="BG219">
+        <v>1.16</v>
+      </c>
+      <c r="BH219">
+        <v>4.3</v>
+      </c>
+      <c r="BI219">
+        <v>1.3</v>
+      </c>
+      <c r="BJ219">
+        <v>3.05</v>
+      </c>
+      <c r="BK219">
+        <v>1.5</v>
+      </c>
+      <c r="BL219">
+        <v>2.35</v>
+      </c>
+      <c r="BM219">
+        <v>1.79</v>
+      </c>
+      <c r="BN219">
+        <v>1.9</v>
+      </c>
+      <c r="BO219">
+        <v>2.2</v>
+      </c>
+      <c r="BP219">
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="357">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -736,6 +736,9 @@
     <t>['13', '30', '45+7']</t>
   </si>
   <si>
+    <t>['24', '60', '65']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1443,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP219"/>
+  <dimension ref="A1:BP220"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1905,7 +1908,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2192,7 +2195,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ4">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2317,7 +2320,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2729,7 +2732,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2935,7 +2938,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3347,7 +3350,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3425,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ10">
         <v>1.5</v>
@@ -3759,7 +3762,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4995,7 +4998,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5201,7 +5204,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -6025,7 +6028,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6231,7 +6234,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6518,7 +6521,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ25">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR25">
         <v>1.78</v>
@@ -6849,7 +6852,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7055,7 +7058,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7261,7 +7264,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7339,7 +7342,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ29">
         <v>1.45</v>
@@ -7673,7 +7676,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7879,7 +7882,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8291,7 +8294,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -9115,7 +9118,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9321,7 +9324,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9527,7 +9530,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9733,7 +9736,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9939,7 +9942,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10145,7 +10148,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -11256,7 +11259,7 @@
         <v>2</v>
       </c>
       <c r="AQ48">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR48">
         <v>1.44</v>
@@ -11793,7 +11796,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -11999,7 +12002,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12205,7 +12208,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12617,7 +12620,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -13029,7 +13032,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13107,7 +13110,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ57">
         <v>1.58</v>
@@ -13235,7 +13238,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13441,7 +13444,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13647,7 +13650,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13853,7 +13856,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14059,7 +14062,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14471,7 +14474,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14677,7 +14680,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14883,7 +14886,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14964,7 +14967,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ66">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR66">
         <v>1.43</v>
@@ -15579,7 +15582,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ69">
         <v>2.09</v>
@@ -15913,7 +15916,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16119,7 +16122,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q72">
         <v>1.95</v>
@@ -16325,7 +16328,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16531,7 +16534,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16737,7 +16740,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16943,7 +16946,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17149,7 +17152,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17561,7 +17564,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17767,7 +17770,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18179,7 +18182,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18591,7 +18594,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18672,7 +18675,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ84">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR84">
         <v>1.51</v>
@@ -18797,7 +18800,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -19003,7 +19006,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19415,7 +19418,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19493,7 +19496,7 @@
         <v>1.25</v>
       </c>
       <c r="AP88">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ88">
         <v>1.64</v>
@@ -19827,7 +19830,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20033,7 +20036,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -21475,7 +21478,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21681,7 +21684,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -21887,7 +21890,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22299,7 +22302,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22505,7 +22508,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23741,7 +23744,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -23947,7 +23950,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24153,7 +24156,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q111">
         <v>3.25</v>
@@ -24231,7 +24234,7 @@
         <v>1.4</v>
       </c>
       <c r="AP111">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ111">
         <v>1.73</v>
@@ -24359,7 +24362,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24565,7 +24568,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24646,7 +24649,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ113">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR113">
         <v>1.98</v>
@@ -25183,7 +25186,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25389,7 +25392,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25595,7 +25598,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25801,7 +25804,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -26007,7 +26010,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26213,7 +26216,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26419,7 +26422,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26625,7 +26628,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -27243,7 +27246,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27449,7 +27452,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -27939,7 +27942,7 @@
         <v>1.67</v>
       </c>
       <c r="AP129">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ129">
         <v>1.27</v>
@@ -28067,7 +28070,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28479,7 +28482,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28891,7 +28894,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29097,7 +29100,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -29590,7 +29593,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ137">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR137">
         <v>1.42</v>
@@ -30539,7 +30542,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30745,7 +30748,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -31157,7 +31160,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31363,7 +31366,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31569,7 +31572,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31775,7 +31778,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -31981,7 +31984,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32268,7 +32271,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ150">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR150">
         <v>1.48</v>
@@ -32393,7 +32396,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -33011,7 +33014,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33217,7 +33220,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33423,7 +33426,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33629,7 +33632,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33835,7 +33838,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34119,7 +34122,7 @@
         <v>0.14</v>
       </c>
       <c r="AP159">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ159">
         <v>0.5</v>
@@ -34659,7 +34662,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34865,7 +34868,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35071,7 +35074,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35277,7 +35280,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35689,7 +35692,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35770,7 +35773,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ167">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR167">
         <v>1.06</v>
@@ -35895,7 +35898,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36307,7 +36310,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36719,7 +36722,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37337,7 +37340,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -37415,7 +37418,7 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ175">
         <v>1.45</v>
@@ -37955,7 +37958,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38573,7 +38576,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38779,7 +38782,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -38860,7 +38863,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ182">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR182">
         <v>1.74</v>
@@ -39191,7 +39194,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39397,7 +39400,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39603,7 +39606,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -40015,7 +40018,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40221,7 +40224,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40427,7 +40430,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40633,7 +40636,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -41045,7 +41048,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41457,7 +41460,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41663,7 +41666,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -42075,7 +42078,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42281,7 +42284,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42487,7 +42490,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42693,7 +42696,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -42771,7 +42774,7 @@
         <v>1.5</v>
       </c>
       <c r="AP201">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ201">
         <v>1.58</v>
@@ -42899,7 +42902,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43105,7 +43108,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43311,7 +43314,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43517,7 +43520,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -43804,7 +43807,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ206">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR206">
         <v>1.56</v>
@@ -43929,7 +43932,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44341,7 +44344,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44753,7 +44756,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -44959,7 +44962,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45165,7 +45168,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45371,7 +45374,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45577,7 +45580,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -45783,7 +45786,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -45989,7 +45992,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46195,7 +46198,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46401,7 +46404,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46558,6 +46561,212 @@
       </c>
       <c r="BP219">
         <v>1.58</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7466893</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45677.70833333334</v>
+      </c>
+      <c r="F220">
+        <v>22</v>
+      </c>
+      <c r="G220" t="s">
+        <v>78</v>
+      </c>
+      <c r="H220" t="s">
+        <v>87</v>
+      </c>
+      <c r="I220">
+        <v>1</v>
+      </c>
+      <c r="J220">
+        <v>1</v>
+      </c>
+      <c r="K220">
+        <v>2</v>
+      </c>
+      <c r="L220">
+        <v>3</v>
+      </c>
+      <c r="M220">
+        <v>1</v>
+      </c>
+      <c r="N220">
+        <v>4</v>
+      </c>
+      <c r="O220" t="s">
+        <v>240</v>
+      </c>
+      <c r="P220" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q220">
+        <v>1.73</v>
+      </c>
+      <c r="R220">
+        <v>2.88</v>
+      </c>
+      <c r="S220">
+        <v>6.5</v>
+      </c>
+      <c r="T220">
+        <v>1.2</v>
+      </c>
+      <c r="U220">
+        <v>4.33</v>
+      </c>
+      <c r="V220">
+        <v>1.91</v>
+      </c>
+      <c r="W220">
+        <v>1.8</v>
+      </c>
+      <c r="X220">
+        <v>4</v>
+      </c>
+      <c r="Y220">
+        <v>1.22</v>
+      </c>
+      <c r="Z220">
+        <v>1.36</v>
+      </c>
+      <c r="AA220">
+        <v>5.6</v>
+      </c>
+      <c r="AB220">
+        <v>6.5</v>
+      </c>
+      <c r="AC220">
+        <v>1.01</v>
+      </c>
+      <c r="AD220">
+        <v>34</v>
+      </c>
+      <c r="AE220">
+        <v>1.1</v>
+      </c>
+      <c r="AF220">
+        <v>7.6</v>
+      </c>
+      <c r="AG220">
+        <v>1.36</v>
+      </c>
+      <c r="AH220">
+        <v>3.1</v>
+      </c>
+      <c r="AI220">
+        <v>1.62</v>
+      </c>
+      <c r="AJ220">
+        <v>2.2</v>
+      </c>
+      <c r="AK220">
+        <v>1.09</v>
+      </c>
+      <c r="AL220">
+        <v>1.14</v>
+      </c>
+      <c r="AM220">
+        <v>3.2</v>
+      </c>
+      <c r="AN220">
+        <v>1.6</v>
+      </c>
+      <c r="AO220">
+        <v>0.82</v>
+      </c>
+      <c r="AP220">
+        <v>1.73</v>
+      </c>
+      <c r="AQ220">
+        <v>0.75</v>
+      </c>
+      <c r="AR220">
+        <v>1.85</v>
+      </c>
+      <c r="AS220">
+        <v>1.27</v>
+      </c>
+      <c r="AT220">
+        <v>3.12</v>
+      </c>
+      <c r="AU220">
+        <v>8</v>
+      </c>
+      <c r="AV220">
+        <v>5</v>
+      </c>
+      <c r="AW220">
+        <v>12</v>
+      </c>
+      <c r="AX220">
+        <v>5</v>
+      </c>
+      <c r="AY220">
+        <v>26</v>
+      </c>
+      <c r="AZ220">
+        <v>12</v>
+      </c>
+      <c r="BA220">
+        <v>3</v>
+      </c>
+      <c r="BB220">
+        <v>6</v>
+      </c>
+      <c r="BC220">
+        <v>9</v>
+      </c>
+      <c r="BD220">
+        <v>1.17</v>
+      </c>
+      <c r="BE220">
+        <v>9</v>
+      </c>
+      <c r="BF220">
+        <v>5.4</v>
+      </c>
+      <c r="BG220">
+        <v>1.26</v>
+      </c>
+      <c r="BH220">
+        <v>3.4</v>
+      </c>
+      <c r="BI220">
+        <v>1.44</v>
+      </c>
+      <c r="BJ220">
+        <v>2.55</v>
+      </c>
+      <c r="BK220">
+        <v>1.73</v>
+      </c>
+      <c r="BL220">
+        <v>1.96</v>
+      </c>
+      <c r="BM220">
+        <v>2.15</v>
+      </c>
+      <c r="BN220">
+        <v>1.61</v>
+      </c>
+      <c r="BO220">
+        <v>2.7</v>
+      </c>
+      <c r="BP220">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
